--- a/database/event/2572/event_2572_evp_summary.xlsx
+++ b/database/event/2572/event_2572_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.4983</v>
+        <v>4.9997</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6931</v>
+        <v>0.7704</v>
       </c>
       <c r="D2" t="n">
-        <v>1.3959</v>
+        <v>1.548</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4983</v>
+        <v>4.9997</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2653</v>
+        <v>2.7667</v>
       </c>
       <c r="G2" t="n">
         <v>2.233</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2653</v>
+        <v>2.7667</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8361</v>
+        <v>2.2425</v>
       </c>
       <c r="J2" t="n">
         <v>2.233</v>
@@ -529,7 +529,7 @@
         <v>57</v>
       </c>
       <c r="M2" t="n">
-        <v>4.069100000000001</v>
+        <v>4.4755</v>
       </c>
       <c r="N2" t="n">
         <v>107</v>
@@ -538,127 +538,127 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.7222</v>
+        <v>3.7984</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5736</v>
+        <v>0.5853</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0823</v>
+        <v>1.0694</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7222</v>
+        <v>3.7984</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7638</v>
+        <v>2.6686</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0416</v>
+        <v>1.1298</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7638</v>
+        <v>2.6686</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0507</v>
+        <v>2.163</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0416</v>
+        <v>1.1298</v>
       </c>
       <c r="K3" t="n">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="L3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M3" t="n">
-        <v>3.0091</v>
+        <v>3.2928</v>
       </c>
       <c r="N3" t="n">
-        <v>148</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Rickeh</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.5899</v>
+        <v>3.7262</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5532</v>
+        <v>0.5742</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0289</v>
+        <v>1.0406</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5899</v>
+        <v>3.7262</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2244</v>
+        <v>3.7678</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3655</v>
+        <v>-0.0416</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2244</v>
+        <v>3.7678</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6135</v>
+        <v>3.0539</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3655</v>
+        <v>-0.0416</v>
       </c>
       <c r="K4" t="n">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="L4" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="M4" t="n">
-        <v>2.979</v>
+        <v>3.0123</v>
       </c>
       <c r="N4" t="n">
-        <v>171</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>Rickeh</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.4411</v>
+        <v>3.5899</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5302</v>
+        <v>0.5532</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9688</v>
+        <v>0.9863</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4411</v>
+        <v>3.5899</v>
       </c>
       <c r="F5" t="n">
-        <v>3.9309</v>
+        <v>3.2244</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4898</v>
+        <v>0.3655</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9309</v>
+        <v>3.2244</v>
       </c>
       <c r="I5" t="n">
-        <v>3.1861</v>
+        <v>2.6135</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4898</v>
+        <v>0.3655</v>
       </c>
       <c r="K5" t="n">
         <v>115</v>
@@ -667,7 +667,7 @@
         <v>56</v>
       </c>
       <c r="M5" t="n">
-        <v>2.6963</v>
+        <v>2.979</v>
       </c>
       <c r="N5" t="n">
         <v>171</v>
@@ -676,47 +676,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.3415</v>
+        <v>3.4411</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5149</v>
+        <v>0.5302</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9285</v>
+        <v>0.927</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3415</v>
+        <v>3.4411</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2117</v>
+        <v>3.9309</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1298</v>
+        <v>-0.4898</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2117</v>
+        <v>3.9309</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7927</v>
+        <v>3.1861</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1298</v>
+        <v>-0.4898</v>
       </c>
       <c r="K6" t="n">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="L6" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9225</v>
+        <v>2.6963</v>
       </c>
       <c r="N6" t="n">
-        <v>107</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7">
@@ -732,7 +732,7 @@
         <v>0.4706</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8125</v>
+        <v>0.7729</v>
       </c>
       <c r="E7" t="n">
         <v>3.0542</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.8101</v>
+        <v>3.0263</v>
       </c>
       <c r="C8" t="n">
-        <v>0.433</v>
+        <v>0.4663</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7139</v>
+        <v>0.7618</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8101</v>
+        <v>3.0263</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2382</v>
+        <v>3.4544</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4281</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2382</v>
+        <v>3.4544</v>
       </c>
       <c r="I8" t="n">
-        <v>2.6247</v>
+        <v>2.7999</v>
       </c>
       <c r="J8" t="n">
         <v>-0.4281</v>
@@ -805,7 +805,7 @@
         <v>49</v>
       </c>
       <c r="M8" t="n">
-        <v>2.1966</v>
+        <v>2.3718</v>
       </c>
       <c r="N8" t="n">
         <v>148</v>
@@ -814,44 +814,44 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.7097</v>
+        <v>2.8402</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4175</v>
+        <v>0.4376</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6733</v>
+        <v>0.6876</v>
       </c>
       <c r="E9" t="n">
-        <v>2.7097</v>
+        <v>2.8402</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6313</v>
+        <v>2.868</v>
       </c>
       <c r="G9" t="n">
-        <v>2.0784</v>
+        <v>-0.0278</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6313</v>
+        <v>2.868</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5117</v>
+        <v>2.3246</v>
       </c>
       <c r="J9" t="n">
-        <v>2.0784</v>
+        <v>-0.0278</v>
       </c>
       <c r="K9" t="n">
+        <v>50</v>
+      </c>
+      <c r="L9" t="n">
         <v>57</v>
       </c>
-      <c r="L9" t="n">
-        <v>50</v>
-      </c>
       <c r="M9" t="n">
-        <v>2.5901</v>
+        <v>2.2968</v>
       </c>
       <c r="N9" t="n">
         <v>107</v>
@@ -860,47 +860,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6824</v>
+        <v>2.7097</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4133</v>
+        <v>0.4175</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6623</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6824</v>
+        <v>2.7097</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8287</v>
+        <v>0.6313</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1463</v>
+        <v>2.0784</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8287</v>
+        <v>0.6313</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2927</v>
+        <v>0.5117</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1463</v>
+        <v>2.0784</v>
       </c>
       <c r="K10" t="n">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="L10" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M10" t="n">
-        <v>2.1464</v>
+        <v>2.5901</v>
       </c>
       <c r="N10" t="n">
-        <v>171</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11">
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6187</v>
+        <v>2.7014</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4035</v>
+        <v>0.4163</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6365</v>
+        <v>0.6323</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6187</v>
+        <v>2.7014</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5411</v>
+        <v>1.6238</v>
       </c>
       <c r="G11" t="n">
         <v>1.0776</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5411</v>
+        <v>1.6238</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2491</v>
+        <v>1.3161</v>
       </c>
       <c r="J11" t="n">
         <v>1.0776</v>
@@ -943,7 +943,7 @@
         <v>57</v>
       </c>
       <c r="M11" t="n">
-        <v>2.3267</v>
+        <v>2.3937</v>
       </c>
       <c r="N11" t="n">
         <v>107</v>
@@ -952,81 +952,81 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5065</v>
+        <v>2.6824</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3862</v>
+        <v>0.4133</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.6248</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5065</v>
+        <v>2.6824</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1453</v>
+        <v>2.8287</v>
       </c>
       <c r="G12" t="n">
-        <v>1.3612</v>
+        <v>-0.1463</v>
       </c>
       <c r="H12" t="n">
-        <v>1.1453</v>
+        <v>2.8287</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9283</v>
+        <v>2.2927</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3612</v>
+        <v>-0.1463</v>
       </c>
       <c r="K12" t="n">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="L12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2895</v>
+        <v>2.1464</v>
       </c>
       <c r="N12" t="n">
-        <v>107</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.3211</v>
+        <v>2.5065</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3577</v>
+        <v>0.3862</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5163</v>
+        <v>0.5547</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3211</v>
+        <v>2.5065</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9287</v>
+        <v>1.1453</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3924</v>
+        <v>1.3612</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9287</v>
+        <v>1.1453</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7527</v>
+        <v>0.9283</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3924</v>
+        <v>1.3612</v>
       </c>
       <c r="K13" t="n">
         <v>57</v>
@@ -1035,7 +1035,7 @@
         <v>50</v>
       </c>
       <c r="M13" t="n">
-        <v>2.1451</v>
+        <v>2.2895</v>
       </c>
       <c r="N13" t="n">
         <v>107</v>
@@ -1044,44 +1044,44 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.2751</v>
+        <v>2.3211</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3506</v>
+        <v>0.3577</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4977</v>
+        <v>0.4808</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2751</v>
+        <v>2.3211</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3029</v>
+        <v>0.9287</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0278</v>
+        <v>1.3924</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3029</v>
+        <v>0.9287</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8665</v>
+        <v>0.7527</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0278</v>
+        <v>1.3924</v>
       </c>
       <c r="K14" t="n">
+        <v>57</v>
+      </c>
+      <c r="L14" t="n">
         <v>50</v>
       </c>
-      <c r="L14" t="n">
-        <v>57</v>
-      </c>
       <c r="M14" t="n">
-        <v>1.8387</v>
+        <v>2.1451</v>
       </c>
       <c r="N14" t="n">
         <v>107</v>
@@ -1090,127 +1090,127 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>SZPERO</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9939</v>
+        <v>2.2288</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3072</v>
+        <v>0.3434</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3841</v>
+        <v>0.444</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9939</v>
+        <v>2.2288</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4264</v>
+        <v>2.2288</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4325</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4264</v>
+        <v>2.2288</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9666</v>
+        <v>2.2288</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4325</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L15" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5341</v>
+        <v>2.2288</v>
       </c>
       <c r="N15" t="n">
-        <v>148</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SZPERO</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.936</v>
+        <v>2.218</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2983</v>
+        <v>0.3418</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3607</v>
+        <v>0.4397</v>
       </c>
       <c r="E16" t="n">
-        <v>1.936</v>
+        <v>2.218</v>
       </c>
       <c r="F16" t="n">
-        <v>1.936</v>
+        <v>2.2409</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.0229</v>
       </c>
       <c r="H16" t="n">
-        <v>1.936</v>
+        <v>2.2409</v>
       </c>
       <c r="I16" t="n">
-        <v>1.936</v>
+        <v>1.8163</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.0229</v>
       </c>
       <c r="K16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M16" t="n">
-        <v>1.936</v>
+        <v>1.7934</v>
       </c>
       <c r="N16" t="n">
-        <v>100</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9096</v>
+        <v>2.0939</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2942</v>
+        <v>0.3226</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3501</v>
+        <v>0.3903</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9096</v>
+        <v>2.0939</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9325</v>
+        <v>2.5264</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0229</v>
+        <v>-0.4325</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9325</v>
+        <v>2.5264</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5664</v>
+        <v>2.0477</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0229</v>
+        <v>-0.4325</v>
       </c>
       <c r="K17" t="n">
         <v>99</v>
@@ -1219,7 +1219,7 @@
         <v>49</v>
       </c>
       <c r="M17" t="n">
-        <v>1.5435</v>
+        <v>1.6152</v>
       </c>
       <c r="N17" t="n">
         <v>148</v>
@@ -1228,44 +1228,44 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8336</v>
+        <v>1.9543</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2825</v>
+        <v>0.3011</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3194</v>
+        <v>0.3347</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8336</v>
+        <v>1.9543</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8659</v>
+        <v>1.6912</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6995</v>
+        <v>0.2631</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8659</v>
+        <v>1.6912</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7018</v>
+        <v>1.3708</v>
       </c>
       <c r="J18" t="n">
-        <v>2.6995</v>
+        <v>0.2631</v>
       </c>
       <c r="K18" t="n">
+        <v>50</v>
+      </c>
+      <c r="L18" t="n">
         <v>57</v>
       </c>
-      <c r="L18" t="n">
-        <v>50</v>
-      </c>
       <c r="M18" t="n">
-        <v>1.9977</v>
+        <v>1.6339</v>
       </c>
       <c r="N18" t="n">
         <v>107</v>
@@ -1274,44 +1274,44 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.6795</v>
+        <v>1.8336</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2588</v>
+        <v>0.2825</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2571</v>
+        <v>0.2866</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6795</v>
+        <v>1.8336</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4164</v>
+        <v>-0.8659</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2631</v>
+        <v>2.6995</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4164</v>
+        <v>-0.8659</v>
       </c>
       <c r="I19" t="n">
-        <v>1.148</v>
+        <v>-0.7018</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2631</v>
+        <v>2.6995</v>
       </c>
       <c r="K19" t="n">
+        <v>57</v>
+      </c>
+      <c r="L19" t="n">
         <v>50</v>
       </c>
-      <c r="L19" t="n">
-        <v>57</v>
-      </c>
       <c r="M19" t="n">
-        <v>1.4111</v>
+        <v>1.9977</v>
       </c>
       <c r="N19" t="n">
         <v>107</v>
@@ -1330,7 +1330,7 @@
         <v>0.2188</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1522</v>
+        <v>0.1218</v>
       </c>
       <c r="E20" t="n">
         <v>1.4199</v>
@@ -1376,7 +1376,7 @@
         <v>0.2085</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1253</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="E21" t="n">
         <v>1.3532</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7537</v>
+        <v>0.7683</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1161</v>
+        <v>0.1184</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1169</v>
+        <v>-0.1378</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7537</v>
+        <v>0.7683</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7537</v>
+        <v>0.7683</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7537</v>
+        <v>0.7683</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7537</v>
+        <v>0.7683</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7537</v>
+        <v>0.7683</v>
       </c>
       <c r="N22" t="n">
         <v>76</v>
@@ -1458,32 +1458,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>rallen</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4722</v>
+        <v>0.5254</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0728</v>
+        <v>0.081</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2306</v>
+        <v>-0.2346</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4722</v>
+        <v>0.5254</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4722</v>
+        <v>0.5254</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4722</v>
+        <v>0.5254</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4722</v>
+        <v>0.5254</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4722</v>
+        <v>0.5254</v>
       </c>
       <c r="N23" t="n">
         <v>100</v>
@@ -1504,32 +1504,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>mouz</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3132</v>
+        <v>0.4722</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0483</v>
+        <v>0.0728</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2948</v>
+        <v>-0.2558</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3132</v>
+        <v>0.4722</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3132</v>
+        <v>0.4722</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3132</v>
+        <v>0.4722</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3132</v>
+        <v>0.4722</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3132</v>
+        <v>0.4722</v>
       </c>
       <c r="N24" t="n">
         <v>100</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ANDROID</t>
+          <t>mouz</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2746</v>
+        <v>0.4458</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0423</v>
+        <v>0.0687</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3104</v>
+        <v>-0.2663</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2746</v>
+        <v>0.4458</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2746</v>
+        <v>0.4458</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2746</v>
+        <v>0.4458</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2746</v>
+        <v>0.4458</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2746</v>
+        <v>0.4458</v>
       </c>
       <c r="N25" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>rallen</t>
+          <t>ANDROID</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0217</v>
+        <v>0.2746</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0033</v>
+        <v>0.0423</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4126</v>
+        <v>-0.3345</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0217</v>
+        <v>0.2746</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0217</v>
+        <v>0.2746</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0217</v>
+        <v>0.2746</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0217</v>
+        <v>0.2746</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0217</v>
+        <v>0.2746</v>
       </c>
       <c r="N26" t="n">
-        <v>100</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0035</v>
+        <v>0.1832</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0005</v>
+        <v>0.0282</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4199</v>
+        <v>-0.3709</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0035</v>
+        <v>0.1832</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0035</v>
+        <v>0.1832</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0035</v>
+        <v>0.1832</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0035</v>
+        <v>0.1832</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0035</v>
+        <v>0.1832</v>
       </c>
       <c r="N27" t="n">
         <v>100</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0204</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4749</v>
+        <v>-0.4967</v>
       </c>
       <c r="E28" t="n">
         <v>-0.1325</v>
@@ -1744,7 +1744,7 @@
         <v>-0.0288</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4969</v>
+        <v>-0.5184</v>
       </c>
       <c r="E29" t="n">
         <v>-0.1869</v>
@@ -1790,7 +1790,7 @@
         <v>-0.058</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5733</v>
+        <v>-0.5937</v>
       </c>
       <c r="E30" t="n">
         <v>-0.3761</v>
@@ -1836,7 +1836,7 @@
         <v>-0.0862</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6473</v>
+        <v>-0.6667</v>
       </c>
       <c r="E31" t="n">
         <v>-0.5592</v>
@@ -1882,7 +1882,7 @@
         <v>-0.1066</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7008</v>
+        <v>-0.7195</v>
       </c>
       <c r="E32" t="n">
         <v>-0.6918</v>
@@ -1928,7 +1928,7 @@
         <v>-0.1084</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7056</v>
+        <v>-0.7242</v>
       </c>
       <c r="E33" t="n">
         <v>-0.7036</v>
@@ -1974,7 +1974,7 @@
         <v>-0.1098</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7093</v>
+        <v>-0.7279</v>
       </c>
       <c r="E34" t="n">
         <v>-0.7128</v>
@@ -2020,7 +2020,7 @@
         <v>-0.1175</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7295</v>
+        <v>-0.7478</v>
       </c>
       <c r="E35" t="n">
         <v>-0.7628</v>
@@ -2066,7 +2066,7 @@
         <v>-0.1326</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7689</v>
+        <v>-0.7867</v>
       </c>
       <c r="E36" t="n">
         <v>-0.8603</v>
@@ -2112,7 +2112,7 @@
         <v>-0.1469</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8065</v>
+        <v>-0.8237</v>
       </c>
       <c r="E37" t="n">
         <v>-0.9534</v>
@@ -2158,7 +2158,7 @@
         <v>-0.1492</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8125</v>
+        <v>-0.8296</v>
       </c>
       <c r="E38" t="n">
         <v>-0.9681999999999999</v>
@@ -2204,7 +2204,7 @@
         <v>-0.2658</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1183</v>
+        <v>-1.1312</v>
       </c>
       <c r="E39" t="n">
         <v>-1.7252</v>
@@ -2250,7 +2250,7 @@
         <v>-0.2922</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1875</v>
+        <v>-1.1995</v>
       </c>
       <c r="E40" t="n">
         <v>-1.8966</v>
@@ -2296,7 +2296,7 @@
         <v>-0.2972</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2006</v>
+        <v>-1.2124</v>
       </c>
       <c r="E41" t="n">
         <v>-1.9289</v>

--- a/database/event/2572/event_2572_evp_summary.xlsx
+++ b/database/event/2572/event_2572_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.9997</v>
+        <v>4.6868</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7704</v>
+        <v>0.7222</v>
       </c>
       <c r="D2" t="n">
-        <v>1.548</v>
+        <v>1.4778</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9997</v>
+        <v>4.6868</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7667</v>
+        <v>2.7618</v>
       </c>
       <c r="G2" t="n">
-        <v>2.233</v>
+        <v>1.925</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7667</v>
+        <v>4.2446</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2425</v>
+        <v>2.207</v>
       </c>
       <c r="J2" t="n">
-        <v>2.233</v>
+        <v>1.925</v>
       </c>
       <c r="K2" t="n">
         <v>50</v>
@@ -529,7 +529,7 @@
         <v>57</v>
       </c>
       <c r="M2" t="n">
-        <v>4.4755</v>
+        <v>4.132</v>
       </c>
       <c r="N2" t="n">
         <v>107</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.7984</v>
+        <v>3.6412</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5853</v>
+        <v>0.5611</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0694</v>
+        <v>1.0058</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7984</v>
+        <v>3.6412</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6686</v>
+        <v>2.6406</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1298</v>
+        <v>1.0006</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6686</v>
+        <v>3.8176</v>
       </c>
       <c r="I3" t="n">
-        <v>2.163</v>
+        <v>1.985</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1298</v>
+        <v>1.0006</v>
       </c>
       <c r="K3" t="n">
         <v>57</v>
@@ -575,7 +575,7 @@
         <v>50</v>
       </c>
       <c r="M3" t="n">
-        <v>3.2928</v>
+        <v>2.9856</v>
       </c>
       <c r="N3" t="n">
         <v>107</v>
@@ -584,173 +584,173 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>Rickeh</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.7262</v>
+        <v>3.4831</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5742</v>
+        <v>0.5367</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0406</v>
+        <v>0.9344</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7262</v>
+        <v>3.4831</v>
       </c>
       <c r="F4" t="n">
-        <v>3.7678</v>
+        <v>3.1352</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0416</v>
+        <v>0.3479</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7678</v>
+        <v>5.5603</v>
       </c>
       <c r="I4" t="n">
-        <v>3.0539</v>
+        <v>2.8911</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.0416</v>
+        <v>0.3479</v>
       </c>
       <c r="K4" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="L4" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="M4" t="n">
-        <v>3.0123</v>
+        <v>3.239</v>
       </c>
       <c r="N4" t="n">
-        <v>148</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Rickeh</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.5899</v>
+        <v>3.3777</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5532</v>
+        <v>0.5205</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9863</v>
+        <v>0.8868</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5899</v>
+        <v>3.3777</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2244</v>
+        <v>3.4396</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3655</v>
+        <v>-0.0619</v>
       </c>
       <c r="H5" t="n">
-        <v>3.2244</v>
+        <v>6.6327</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6135</v>
+        <v>3.4487</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3655</v>
+        <v>-0.0619</v>
       </c>
       <c r="K5" t="n">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="L5" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="M5" t="n">
-        <v>2.979</v>
+        <v>3.3868</v>
       </c>
       <c r="N5" t="n">
-        <v>171</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>kNgV-</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.4411</v>
+        <v>3.2231</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5302</v>
+        <v>0.4966</v>
       </c>
       <c r="D6" t="n">
-        <v>0.927</v>
+        <v>0.8171</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4411</v>
+        <v>3.2231</v>
       </c>
       <c r="F6" t="n">
-        <v>3.9309</v>
+        <v>2.3464</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4898</v>
+        <v>0.8767</v>
       </c>
       <c r="H6" t="n">
-        <v>3.9309</v>
+        <v>2.781</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1861</v>
+        <v>1.446</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4898</v>
+        <v>0.8767</v>
       </c>
       <c r="K6" t="n">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="L6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M6" t="n">
-        <v>2.6963</v>
+        <v>2.3227</v>
       </c>
       <c r="N6" t="n">
-        <v>171</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.0542</v>
+        <v>3.1264</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4706</v>
+        <v>0.4817</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7729</v>
+        <v>0.7734</v>
       </c>
       <c r="E7" t="n">
-        <v>3.0542</v>
+        <v>3.1264</v>
       </c>
       <c r="F7" t="n">
-        <v>3.618</v>
+        <v>3.4651</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5638</v>
+        <v>-0.3387</v>
       </c>
       <c r="H7" t="n">
-        <v>3.618</v>
+        <v>6.7227</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9325</v>
+        <v>3.4955</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5638</v>
+        <v>-0.3387</v>
       </c>
       <c r="K7" t="n">
         <v>115</v>
@@ -759,7 +759,7 @@
         <v>56</v>
       </c>
       <c r="M7" t="n">
-        <v>2.3687</v>
+        <v>3.1568</v>
       </c>
       <c r="N7" t="n">
         <v>171</v>
@@ -768,127 +768,127 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.0263</v>
+        <v>3.0545</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4663</v>
+        <v>0.4707</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7618</v>
+        <v>0.7409</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0263</v>
+        <v>3.0545</v>
       </c>
       <c r="F8" t="n">
-        <v>3.4544</v>
+        <v>3.443</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4281</v>
+        <v>-0.3885</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4544</v>
+        <v>6.6446</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7999</v>
+        <v>3.4549</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4281</v>
+        <v>-0.3885</v>
       </c>
       <c r="K8" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="L8" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3718</v>
+        <v>3.0664</v>
       </c>
       <c r="N8" t="n">
-        <v>148</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8402</v>
+        <v>3.0521</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4376</v>
+        <v>0.4703</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6876</v>
+        <v>0.7399</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8402</v>
+        <v>3.0521</v>
       </c>
       <c r="F9" t="n">
-        <v>2.868</v>
+        <v>3.2159</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0278</v>
+        <v>-0.1638</v>
       </c>
       <c r="H9" t="n">
-        <v>2.868</v>
+        <v>5.8446</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3246</v>
+        <v>3.0389</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0278</v>
+        <v>-0.1638</v>
       </c>
       <c r="K9" t="n">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="L9" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2968</v>
+        <v>2.8751</v>
       </c>
       <c r="N9" t="n">
-        <v>107</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.7097</v>
+        <v>3.0397</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4175</v>
+        <v>0.4684</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6356000000000001</v>
+        <v>0.7343</v>
       </c>
       <c r="E10" t="n">
-        <v>2.7097</v>
+        <v>3.0397</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6313</v>
+        <v>1.8463</v>
       </c>
       <c r="G10" t="n">
-        <v>2.0784</v>
+        <v>1.1934</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6313</v>
+        <v>1.8463</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5117</v>
+        <v>0.96</v>
       </c>
       <c r="J10" t="n">
-        <v>2.0784</v>
+        <v>1.1934</v>
       </c>
       <c r="K10" t="n">
         <v>57</v>
@@ -897,7 +897,7 @@
         <v>50</v>
       </c>
       <c r="M10" t="n">
-        <v>2.5901</v>
+        <v>2.1534</v>
       </c>
       <c r="N10" t="n">
         <v>107</v>
@@ -906,44 +906,44 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kNgV-</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.7014</v>
+        <v>3.0259</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4163</v>
+        <v>0.4663</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6323</v>
+        <v>0.728</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7014</v>
+        <v>3.0259</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6238</v>
+        <v>1.5653</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0776</v>
+        <v>1.4606</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6238</v>
+        <v>1.5653</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3161</v>
+        <v>0.8139</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0776</v>
+        <v>1.4606</v>
       </c>
       <c r="K11" t="n">
+        <v>57</v>
+      </c>
+      <c r="L11" t="n">
         <v>50</v>
       </c>
-      <c r="L11" t="n">
-        <v>57</v>
-      </c>
       <c r="M11" t="n">
-        <v>2.3937</v>
+        <v>2.2745</v>
       </c>
       <c r="N11" t="n">
         <v>107</v>
@@ -952,136 +952,136 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.6824</v>
+        <v>2.9161</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4133</v>
+        <v>0.4493</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6248</v>
+        <v>0.6785</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6824</v>
+        <v>2.9161</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8287</v>
+        <v>1.1043</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1463</v>
+        <v>1.8118</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8287</v>
+        <v>1.1043</v>
       </c>
       <c r="I12" t="n">
-        <v>2.2927</v>
+        <v>0.5742</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1463</v>
+        <v>1.8118</v>
       </c>
       <c r="K12" t="n">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="L12" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M12" t="n">
-        <v>2.1464</v>
+        <v>2.386</v>
       </c>
       <c r="N12" t="n">
-        <v>171</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5065</v>
+        <v>2.7477</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3862</v>
+        <v>0.4234</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5547</v>
+        <v>0.6024</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5065</v>
+        <v>2.7477</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1453</v>
+        <v>2.8019</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3612</v>
+        <v>-0.0542</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1453</v>
+        <v>4.386</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9283</v>
+        <v>2.2805</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3612</v>
+        <v>-0.0542</v>
       </c>
       <c r="K13" t="n">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="L13" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M13" t="n">
-        <v>2.2895</v>
+        <v>2.2263</v>
       </c>
       <c r="N13" t="n">
-        <v>107</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3211</v>
+        <v>2.6752</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3577</v>
+        <v>0.4122</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4808</v>
+        <v>0.5697</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3211</v>
+        <v>2.6752</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9287</v>
+        <v>2.709</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3924</v>
+        <v>-0.0338</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9287</v>
+        <v>4.0586</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7527</v>
+        <v>2.1103</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3924</v>
+        <v>-0.0338</v>
       </c>
       <c r="K14" t="n">
+        <v>50</v>
+      </c>
+      <c r="L14" t="n">
         <v>57</v>
       </c>
-      <c r="L14" t="n">
-        <v>50</v>
-      </c>
       <c r="M14" t="n">
-        <v>2.1451</v>
+        <v>2.0765</v>
       </c>
       <c r="N14" t="n">
         <v>107</v>
@@ -1090,47 +1090,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SZPERO</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2288</v>
+        <v>2.6005</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3434</v>
+        <v>0.4007</v>
       </c>
       <c r="D15" t="n">
-        <v>0.444</v>
+        <v>0.536</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2288</v>
+        <v>2.6005</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2288</v>
+        <v>2.3257</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.2748</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2288</v>
+        <v>2.7081</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2288</v>
+        <v>1.4081</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.2748</v>
       </c>
       <c r="K15" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="M15" t="n">
-        <v>2.2288</v>
+        <v>1.6829</v>
       </c>
       <c r="N15" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.218</v>
+        <v>2.5428</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3418</v>
+        <v>0.3918</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4397</v>
+        <v>0.5099</v>
       </c>
       <c r="E16" t="n">
-        <v>2.218</v>
+        <v>2.5428</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2409</v>
+        <v>2.6069</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0229</v>
+        <v>-0.0641</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2409</v>
+        <v>3.6988</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8163</v>
+        <v>1.9232</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0229</v>
+        <v>-0.0641</v>
       </c>
       <c r="K16" t="n">
         <v>99</v>
@@ -1173,7 +1173,7 @@
         <v>49</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7934</v>
+        <v>1.8591</v>
       </c>
       <c r="N16" t="n">
         <v>148</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.0939</v>
+        <v>2.4782</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3226</v>
+        <v>0.3819</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3903</v>
+        <v>0.4808</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0939</v>
+        <v>2.4782</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5264</v>
+        <v>2.7927</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4325</v>
+        <v>-0.3145</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5264</v>
+        <v>4.3535</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0477</v>
+        <v>2.2636</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4325</v>
+        <v>-0.3145</v>
       </c>
       <c r="K17" t="n">
         <v>99</v>
@@ -1219,7 +1219,7 @@
         <v>49</v>
       </c>
       <c r="M17" t="n">
-        <v>1.6152</v>
+        <v>1.9491</v>
       </c>
       <c r="N17" t="n">
         <v>148</v>
@@ -1228,124 +1228,124 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>SZPERO</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9543</v>
+        <v>2.4035</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3011</v>
+        <v>0.3704</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3347</v>
+        <v>0.447</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9543</v>
+        <v>2.4035</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6912</v>
+        <v>2.4035</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2631</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6912</v>
+        <v>2.4035</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3708</v>
+        <v>2.4035</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2631</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L18" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6339</v>
+        <v>2.4035</v>
       </c>
       <c r="N18" t="n">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>SHOOWTiME</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.8336</v>
+        <v>1.6107</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2825</v>
+        <v>0.2482</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2866</v>
+        <v>0.0891</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8336</v>
+        <v>1.6107</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8659</v>
+        <v>1.6107</v>
       </c>
       <c r="G19" t="n">
-        <v>2.6995</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8659</v>
+        <v>1.6107</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7018</v>
+        <v>1.6107</v>
       </c>
       <c r="J19" t="n">
-        <v>2.6995</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>57</v>
+        <v>125</v>
       </c>
       <c r="L19" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.9977</v>
+        <v>1.6107</v>
       </c>
       <c r="N19" t="n">
-        <v>107</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SHOOWTiME</t>
+          <t>yel</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4199</v>
+        <v>1.4695</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2188</v>
+        <v>0.2264</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1218</v>
+        <v>0.0254</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4199</v>
+        <v>1.4695</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4199</v>
+        <v>1.4695</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4199</v>
+        <v>1.4695</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4199</v>
+        <v>1.4695</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4199</v>
+        <v>1.4695</v>
       </c>
       <c r="N20" t="n">
         <v>125</v>
@@ -1366,170 +1366,170 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>yel</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.3532</v>
+        <v>1.2021</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2085</v>
+        <v>0.1852</v>
       </c>
       <c r="D21" t="n">
-        <v>0.09520000000000001</v>
+        <v>-0.0953</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3532</v>
+        <v>1.2021</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3532</v>
+        <v>-1.0784</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2.2805</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3532</v>
+        <v>-1.0784</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3532</v>
+        <v>-0.5607</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>2.2805</v>
       </c>
       <c r="K21" t="n">
-        <v>125</v>
+        <v>57</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3532</v>
+        <v>1.7198</v>
       </c>
       <c r="N21" t="n">
-        <v>125</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>yay</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7683</v>
+        <v>1.188</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1184</v>
+        <v>0.1831</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1378</v>
+        <v>-0.1017</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7683</v>
+        <v>1.188</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7683</v>
+        <v>1.9602</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.7722</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7683</v>
+        <v>1.9602</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7683</v>
+        <v>1.0192</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.7722</v>
       </c>
       <c r="K22" t="n">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7683</v>
+        <v>0.2470000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>76</v>
+        <v>148</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>rallen</t>
+          <t>yay</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5254</v>
+        <v>1.0178</v>
       </c>
       <c r="C23" t="n">
-        <v>0.081</v>
+        <v>0.1568</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2346</v>
+        <v>-0.1785</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5254</v>
+        <v>1.0178</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5254</v>
+        <v>1.0178</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5254</v>
+        <v>1.0178</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5254</v>
+        <v>1.0178</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5254</v>
+        <v>1.0178</v>
       </c>
       <c r="N23" t="n">
-        <v>100</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>mouz</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4722</v>
+        <v>0.976</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0728</v>
+        <v>0.1504</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2558</v>
+        <v>-0.1974</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4722</v>
+        <v>0.976</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4722</v>
+        <v>0.976</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4722</v>
+        <v>0.976</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4722</v>
+        <v>0.976</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4722</v>
+        <v>0.976</v>
       </c>
       <c r="N24" t="n">
         <v>100</v>
@@ -1550,32 +1550,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>mouz</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4458</v>
+        <v>0.8511</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0687</v>
+        <v>0.1311</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2663</v>
+        <v>-0.2538</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4458</v>
+        <v>0.8511</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4458</v>
+        <v>0.8511</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4458</v>
+        <v>0.8511</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4458</v>
+        <v>0.8511</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4458</v>
+        <v>0.8511</v>
       </c>
       <c r="N25" t="n">
         <v>100</v>
@@ -1596,47 +1596,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ANDROID</t>
+          <t>rallen</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2746</v>
+        <v>0.7174</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0423</v>
+        <v>0.1105</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3345</v>
+        <v>-0.3141</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2746</v>
+        <v>0.7174</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2746</v>
+        <v>0.7174</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2746</v>
+        <v>0.7174</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2746</v>
+        <v>0.7174</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2746</v>
+        <v>0.7174</v>
       </c>
       <c r="N26" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1832</v>
+        <v>0.5877</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0282</v>
+        <v>0.0906</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3709</v>
+        <v>-0.3727</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1832</v>
+        <v>0.5877</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1832</v>
+        <v>0.5877</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1832</v>
+        <v>0.5877</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1832</v>
+        <v>0.5877</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1832</v>
+        <v>0.5877</v>
       </c>
       <c r="N27" t="n">
         <v>100</v>
@@ -1688,78 +1688,78 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>ANDROID</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1325</v>
+        <v>0.3753</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0204</v>
+        <v>0.0578</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4967</v>
+        <v>-0.4686</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1325</v>
+        <v>0.3753</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8675</v>
+        <v>0.3753</v>
       </c>
       <c r="G28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.8675</v>
+        <v>0.3753</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.3753</v>
       </c>
       <c r="J28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="L28" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.2969000000000001</v>
+        <v>0.3753</v>
       </c>
       <c r="N28" t="n">
-        <v>148</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NEKIZ</t>
+          <t>PKL</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1869</v>
+        <v>0.1035</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0288</v>
+        <v>0.0159</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5184</v>
+        <v>-0.5913</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1869</v>
+        <v>0.1035</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1869</v>
+        <v>0.1035</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1869</v>
+        <v>0.1035</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1869</v>
+        <v>0.1035</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1869</v>
+        <v>0.1035</v>
       </c>
       <c r="N29" t="n">
         <v>125</v>
@@ -1780,32 +1780,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PKL</t>
+          <t>NEKIZ</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3761</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.058</v>
+        <v>-0.0137</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5937</v>
+        <v>-0.6781</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.3761</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.3761</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.3761</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3761</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3761</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="N30" t="n">
         <v>125</v>
@@ -1826,78 +1826,78 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Chuti</t>
+          <t>dephh</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5592</v>
+        <v>-0.2881</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0862</v>
+        <v>-0.0444</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6667</v>
+        <v>-0.7681</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5592</v>
+        <v>-0.2881</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.5592</v>
+        <v>-0.2881</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.5592</v>
+        <v>-0.2881</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5592</v>
+        <v>-0.2881</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.5592</v>
+        <v>-0.2881</v>
       </c>
       <c r="N31" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>JonY BoY</t>
+          <t>Chuti</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6918</v>
+        <v>-0.3901</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1066</v>
+        <v>-0.0601</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7195</v>
+        <v>-0.8141</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6918</v>
+        <v>-0.3901</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.6918</v>
+        <v>-0.3901</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.6918</v>
+        <v>-0.3901</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6918</v>
+        <v>-0.3901</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.6918</v>
+        <v>-0.3901</v>
       </c>
       <c r="N32" t="n">
         <v>72</v>
@@ -1918,32 +1918,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MarKE</t>
+          <t>JonY BoY</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7036</v>
+        <v>-0.3935</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1084</v>
+        <v>-0.0606</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7242</v>
+        <v>-0.8157</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7036</v>
+        <v>-0.3935</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.7036</v>
+        <v>-0.3935</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.7036</v>
+        <v>-0.3935</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7036</v>
+        <v>-0.3935</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.7036</v>
+        <v>-0.3935</v>
       </c>
       <c r="N33" t="n">
         <v>72</v>
@@ -1964,139 +1964,139 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dephh</t>
+          <t>MarKE</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7128</v>
+        <v>-0.4976</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1098</v>
+        <v>-0.0767</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7279</v>
+        <v>-0.8627</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7128</v>
+        <v>-0.4976</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.7128</v>
+        <v>-0.4976</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7128</v>
+        <v>-0.4976</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.7128</v>
+        <v>-0.4976</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7128</v>
+        <v>-0.4976</v>
       </c>
       <c r="N34" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>guishorro</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7628</v>
+        <v>-0.5285</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1175</v>
+        <v>-0.0814</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7478</v>
+        <v>-0.8766</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7628</v>
+        <v>-0.5285</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7628</v>
+        <v>-0.5285</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7628</v>
+        <v>-0.5285</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7628</v>
+        <v>-0.5285</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7628</v>
+        <v>-0.5285</v>
       </c>
       <c r="N35" t="n">
-        <v>72</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>guishorro</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8603</v>
+        <v>-0.5734</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1326</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7867</v>
+        <v>-0.8969</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8603</v>
+        <v>-0.5734</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.8603</v>
+        <v>-0.5734</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8603</v>
+        <v>-0.5734</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8603</v>
+        <v>-0.5734</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8603</v>
+        <v>-0.5734</v>
       </c>
       <c r="N36" t="n">
-        <v>125</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9534</v>
+        <v>-0.6387</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1469</v>
+        <v>-0.0984</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8237</v>
+        <v>-0.9264</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9534</v>
+        <v>-0.6387</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9534</v>
+        <v>-0.6387</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9534</v>
+        <v>-0.6387</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9534</v>
+        <v>-0.6387</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9534</v>
+        <v>-0.6387</v>
       </c>
       <c r="N37" t="n">
         <v>76</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.9681999999999999</v>
+        <v>-1.0297</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1492</v>
+        <v>-0.1587</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8296</v>
+        <v>-1.1029</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9681999999999999</v>
+        <v>-1.0297</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.6647999999999999</v>
+        <v>-0.753</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.3034</v>
+        <v>-0.2767</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.6647999999999999</v>
+        <v>-0.753</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.5387999999999999</v>
+        <v>-0.3915</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.3034</v>
+        <v>-0.2767</v>
       </c>
       <c r="K38" t="n">
         <v>50</v>
@@ -2185,7 +2185,7 @@
         <v>57</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.8421999999999999</v>
+        <v>-0.6682</v>
       </c>
       <c r="N38" t="n">
         <v>107</v>
@@ -2194,139 +2194,139 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>tutehen</t>
+          <t>Slemmy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.7252</v>
+        <v>-1.4539</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2658</v>
+        <v>-0.224</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1312</v>
+        <v>-1.2944</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.7252</v>
+        <v>-1.4539</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.7252</v>
+        <v>-1.4539</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.7252</v>
+        <v>-1.4539</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.7252</v>
+        <v>-1.4539</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.7252</v>
+        <v>-1.4539</v>
       </c>
       <c r="N39" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FNS</t>
+          <t>tutehen</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.8966</v>
+        <v>-1.4897</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2922</v>
+        <v>-0.2295</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1995</v>
+        <v>-1.3105</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.8966</v>
+        <v>-1.4897</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.2164</v>
+        <v>-1.4897</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.6802</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.2164</v>
+        <v>-1.4897</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.9859</v>
+        <v>-1.4897</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.6802</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="L40" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.6661</v>
+        <v>-1.4897</v>
       </c>
       <c r="N40" t="n">
-        <v>171</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Slemmy</t>
+          <t>FNS</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.9289</v>
+        <v>-1.5595</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2972</v>
+        <v>-0.2403</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2124</v>
+        <v>-1.3421</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.9289</v>
+        <v>-1.5595</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.9289</v>
+        <v>-1.0991</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>-0.4604</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.9289</v>
+        <v>-1.0991</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.9289</v>
+        <v>-0.5715</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>-0.4604</v>
       </c>
       <c r="K41" t="n">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.9289</v>
+        <v>-1.0319</v>
       </c>
       <c r="N41" t="n">
-        <v>76</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -2429,10 +2429,10 @@
         <v>1.3</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5526</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5526</v>
+        <v>0.6578000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.95</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0774</v>
+        <v>-0.0679</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0774</v>
+        <v>-0.0679</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.85</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2789</v>
+        <v>-0.1772</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2789</v>
+        <v>-0.1772</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.78</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3884</v>
+        <v>-0.2477</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3884</v>
+        <v>-0.2477</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.66</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5543</v>
+        <v>-0.3631</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5543</v>
+        <v>-0.3631</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.47</v>
       </c>
       <c r="I7" t="n">
-        <v>1.126</v>
+        <v>1.0875</v>
       </c>
       <c r="J7" t="n">
-        <v>1.126</v>
+        <v>1.0875</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.36</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8891</v>
+        <v>0.9093</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8891</v>
+        <v>0.9093</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.33</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8194</v>
+        <v>0.8435</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8194</v>
+        <v>0.8435</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.18</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4187</v>
+        <v>0.498</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4187</v>
+        <v>0.498</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.02</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0481</v>
+        <v>0.0298</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0481</v>
+        <v>0.0298</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>2.1</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9881</v>
+        <v>1.5334</v>
       </c>
       <c r="J12" t="n">
-        <v>43.7382</v>
+        <v>33.7348</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.41</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.7232</v>
       </c>
       <c r="J13" t="n">
-        <v>20.658</v>
+        <v>15.9104</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.22</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4722</v>
+        <v>0.4752</v>
       </c>
       <c r="J14" t="n">
-        <v>10.3884</v>
+        <v>10.4544</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.11</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1967</v>
+        <v>0.2896</v>
       </c>
       <c r="J15" t="n">
-        <v>4.3274</v>
+        <v>6.3712</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.05</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0244</v>
+        <v>0.1107</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5368000000000001</v>
+        <v>2.4354</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0191</v>
+        <v>-0.0477</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4202</v>
+        <v>-1.0494</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.89</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1088</v>
+        <v>-0.1093</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.3936</v>
+        <v>-2.4046</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.242</v>
+        <v>-0.197</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.324</v>
+        <v>-4.334</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.58</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6163999999999999</v>
+        <v>-0.4137</v>
       </c>
       <c r="J20" t="n">
-        <v>-13.5608</v>
+        <v>-9.1014</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.46</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7712</v>
+        <v>-0.5255</v>
       </c>
       <c r="J21" t="n">
-        <v>-16.9664</v>
+        <v>-11.561</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.62</v>
       </c>
       <c r="I22" t="n">
-        <v>1.463</v>
+        <v>1.0242</v>
       </c>
       <c r="J22" t="n">
-        <v>39.501</v>
+        <v>27.6534</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.36</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9371</v>
+        <v>0.6884</v>
       </c>
       <c r="J23" t="n">
-        <v>25.3017</v>
+        <v>18.5868</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.18</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4789</v>
+        <v>0.4406</v>
       </c>
       <c r="J24" t="n">
-        <v>12.9303</v>
+        <v>11.8962</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.92</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4146</v>
+        <v>-0.3404</v>
       </c>
       <c r="J25" t="n">
-        <v>-11.1942</v>
+        <v>-9.190799999999999</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.84</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6286</v>
+        <v>-0.5661</v>
       </c>
       <c r="J26" t="n">
-        <v>-16.9722</v>
+        <v>-15.2847</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.16</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3431</v>
+        <v>0.3617</v>
       </c>
       <c r="J27" t="n">
-        <v>9.2637</v>
+        <v>9.7659</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.01</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0672</v>
+        <v>0.0474</v>
       </c>
       <c r="J28" t="n">
-        <v>1.8144</v>
+        <v>1.2798</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.99</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0038</v>
+        <v>-0.0164</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.1026</v>
+        <v>-0.4428</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1905</v>
+        <v>-0.1175</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.1435</v>
+        <v>-3.1725</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.67</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5495</v>
+        <v>-0.3585</v>
       </c>
       <c r="J31" t="n">
-        <v>-14.8365</v>
+        <v>-9.679500000000001</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.32</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9081</v>
+        <v>0.659</v>
       </c>
       <c r="J32" t="n">
-        <v>27.243</v>
+        <v>19.77</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.16</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5175</v>
+        <v>0.4252</v>
       </c>
       <c r="J33" t="n">
-        <v>15.525</v>
+        <v>12.756</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.12</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4038</v>
+        <v>0.3626</v>
       </c>
       <c r="J34" t="n">
-        <v>12.114</v>
+        <v>10.878</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.98</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1692</v>
+        <v>-0.1119</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.076</v>
+        <v>-3.357</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.79</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7186</v>
+        <v>-0.6685</v>
       </c>
       <c r="J36" t="n">
-        <v>-21.558</v>
+        <v>-20.055</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.05</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1613</v>
+        <v>0.1543</v>
       </c>
       <c r="J37" t="n">
-        <v>4.839</v>
+        <v>4.629</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.04</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1412</v>
+        <v>0.1304</v>
       </c>
       <c r="J38" t="n">
-        <v>4.236</v>
+        <v>3.912</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.01</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0716</v>
+        <v>0.0498</v>
       </c>
       <c r="J39" t="n">
-        <v>2.148</v>
+        <v>1.494</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.82</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3374</v>
+        <v>-0.2115</v>
       </c>
       <c r="J40" t="n">
-        <v>-10.122</v>
+        <v>-6.345</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.77</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4114</v>
+        <v>-0.2613</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.342</v>
+        <v>-7.839</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.52</v>
       </c>
       <c r="I42" t="n">
-        <v>1.2281</v>
+        <v>0.8772</v>
       </c>
       <c r="J42" t="n">
-        <v>31.9306</v>
+        <v>22.8072</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.33</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8207</v>
+        <v>0.6344</v>
       </c>
       <c r="J43" t="n">
-        <v>21.3382</v>
+        <v>16.4944</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.31</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7723</v>
+        <v>0.6082</v>
       </c>
       <c r="J44" t="n">
-        <v>20.0798</v>
+        <v>15.8132</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.28</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.569</v>
       </c>
       <c r="J45" t="n">
-        <v>18.0466</v>
+        <v>14.794</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.91</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4679</v>
+        <v>-0.3911</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.1654</v>
+        <v>-10.1686</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.06</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2243</v>
+        <v>0.2175</v>
       </c>
       <c r="J47" t="n">
-        <v>5.8318</v>
+        <v>5.655</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.89</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1524</v>
+        <v>-0.1272</v>
       </c>
       <c r="J48" t="n">
-        <v>-3.9624</v>
+        <v>-3.3072</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.89</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1524</v>
+        <v>-0.1272</v>
       </c>
       <c r="J49" t="n">
-        <v>-3.9624</v>
+        <v>-3.3072</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3076</v>
+        <v>-0.2085</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.9976</v>
+        <v>-5.421</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.49</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.7518</v>
+        <v>-0.5102</v>
       </c>
       <c r="J51" t="n">
-        <v>-19.5468</v>
+        <v>-13.2652</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.71</v>
       </c>
       <c r="I52" t="n">
-        <v>1.6316</v>
+        <v>1.4114</v>
       </c>
       <c r="J52" t="n">
-        <v>45.6848</v>
+        <v>39.5192</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.14</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3626</v>
+        <v>0.4153</v>
       </c>
       <c r="J53" t="n">
-        <v>10.1528</v>
+        <v>11.6284</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.13</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3337</v>
+        <v>0.389</v>
       </c>
       <c r="J54" t="n">
-        <v>9.3436</v>
+        <v>10.892</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.98</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2164</v>
+        <v>-0.1396</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.0592</v>
+        <v>-3.9088</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3533</v>
+        <v>-0.2776</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.8924</v>
+        <v>-7.7728</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.24</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4815</v>
+        <v>0.5599</v>
       </c>
       <c r="J57" t="n">
-        <v>13.482</v>
+        <v>15.6772</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.16</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3669</v>
+        <v>0.4062</v>
       </c>
       <c r="J58" t="n">
-        <v>10.2732</v>
+        <v>11.3736</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.88</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2107</v>
+        <v>-0.1439</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.8996</v>
+        <v>-4.0292</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.6</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.6264</v>
+        <v>-0.416</v>
       </c>
       <c r="J60" t="n">
-        <v>-17.5392</v>
+        <v>-11.648</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.54</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7007</v>
+        <v>-0.4712</v>
       </c>
       <c r="J61" t="n">
-        <v>-19.6196</v>
+        <v>-13.1936</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.59</v>
       </c>
       <c r="I62" t="n">
-        <v>1.2764</v>
+        <v>1.2029</v>
       </c>
       <c r="J62" t="n">
-        <v>26.8044</v>
+        <v>25.2609</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.54</v>
       </c>
       <c r="I63" t="n">
-        <v>1.1751</v>
+        <v>1.1441</v>
       </c>
       <c r="J63" t="n">
-        <v>24.6771</v>
+        <v>24.0261</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.43</v>
       </c>
       <c r="I64" t="n">
-        <v>0.914</v>
+        <v>1.0089</v>
       </c>
       <c r="J64" t="n">
-        <v>19.194</v>
+        <v>21.1869</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.4</v>
       </c>
       <c r="I65" t="n">
-        <v>0.8462</v>
+        <v>0.9584</v>
       </c>
       <c r="J65" t="n">
-        <v>17.7702</v>
+        <v>20.1264</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.35</v>
       </c>
       <c r="I66" t="n">
-        <v>0.7356</v>
+        <v>0.8551</v>
       </c>
       <c r="J66" t="n">
-        <v>15.4476</v>
+        <v>17.9571</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>0.0474</v>
+        <v>0.0012</v>
       </c>
       <c r="J67" t="n">
-        <v>0.9954</v>
+        <v>0.0252</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.82</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1568</v>
+        <v>-0.15</v>
       </c>
       <c r="J68" t="n">
-        <v>-3.2928</v>
+        <v>-3.15</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.66</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.4067</v>
+        <v>-0.3195</v>
       </c>
       <c r="J69" t="n">
-        <v>-8.540699999999999</v>
+        <v>-6.7095</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.48</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.7083</v>
+        <v>-0.4846</v>
       </c>
       <c r="J70" t="n">
-        <v>-14.8743</v>
+        <v>-10.1766</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.12</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.1529</v>
+        <v>-0.8304</v>
       </c>
       <c r="J71" t="n">
-        <v>-24.2109</v>
+        <v>-17.4384</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.26</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5049</v>
+        <v>0.592</v>
       </c>
       <c r="J72" t="n">
-        <v>13.6323</v>
+        <v>15.984</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.9</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.1718</v>
+        <v>-0.124</v>
       </c>
       <c r="J73" t="n">
-        <v>-4.6386</v>
+        <v>-3.348</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.82</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.3223</v>
+        <v>-0.2061</v>
       </c>
       <c r="J74" t="n">
-        <v>-8.7021</v>
+        <v>-5.5647</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3382</v>
+        <v>-0.2161</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.131399999999999</v>
+        <v>-5.8347</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.68</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5248</v>
+        <v>-0.3424</v>
       </c>
       <c r="J76" t="n">
-        <v>-14.1696</v>
+        <v>-9.2448</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.3</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8349</v>
+        <v>0.8179</v>
       </c>
       <c r="J77" t="n">
-        <v>22.5423</v>
+        <v>22.0833</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.21</v>
       </c>
       <c r="I78" t="n">
-        <v>0.6172</v>
+        <v>0.6008</v>
       </c>
       <c r="J78" t="n">
-        <v>16.6644</v>
+        <v>16.2216</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.15</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4532</v>
+        <v>0.45</v>
       </c>
       <c r="J79" t="n">
-        <v>12.2364</v>
+        <v>12.15</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.12</v>
       </c>
       <c r="I80" t="n">
-        <v>0.3496</v>
+        <v>0.373</v>
       </c>
       <c r="J80" t="n">
-        <v>9.4392</v>
+        <v>10.071</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.84</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.611</v>
+        <v>-0.5507</v>
       </c>
       <c r="J81" t="n">
-        <v>-16.497</v>
+        <v>-14.8689</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.3</v>
       </c>
       <c r="I82" t="n">
-        <v>0.525</v>
+        <v>0.6226</v>
       </c>
       <c r="J82" t="n">
-        <v>13.65</v>
+        <v>16.1876</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.05</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1415</v>
+        <v>0.1422</v>
       </c>
       <c r="J83" t="n">
-        <v>3.679</v>
+        <v>3.6972</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.99</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.0262</v>
+        <v>-0.0198</v>
       </c>
       <c r="J84" t="n">
-        <v>-0.6812</v>
+        <v>-0.5148</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.8</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3803</v>
+        <v>-0.2374</v>
       </c>
       <c r="J85" t="n">
-        <v>-9.8878</v>
+        <v>-6.1724</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.79</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3947</v>
+        <v>-0.2474</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.2622</v>
+        <v>-6.4324</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.43</v>
       </c>
       <c r="I87" t="n">
-        <v>1.0923</v>
+        <v>1.0567</v>
       </c>
       <c r="J87" t="n">
-        <v>28.3998</v>
+        <v>27.4742</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.31</v>
       </c>
       <c r="I88" t="n">
-        <v>0.83</v>
+        <v>0.8243</v>
       </c>
       <c r="J88" t="n">
-        <v>21.58</v>
+        <v>21.4318</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.28</v>
       </c>
       <c r="I89" t="n">
-        <v>0.7597</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="J89" t="n">
-        <v>19.7522</v>
+        <v>19.617</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.08</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1898</v>
+        <v>0.251</v>
       </c>
       <c r="J90" t="n">
-        <v>4.9348</v>
+        <v>6.526</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.77</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.7936</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="J91" t="n">
-        <v>-20.6336</v>
+        <v>-19.383</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.2</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3878</v>
+        <v>0.4426</v>
       </c>
       <c r="J92" t="n">
-        <v>11.2462</v>
+        <v>12.8354</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.04</v>
       </c>
       <c r="I93" t="n">
-        <v>0.12</v>
+        <v>0.1184</v>
       </c>
       <c r="J93" t="n">
-        <v>3.48</v>
+        <v>3.4336</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.93</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1698</v>
+        <v>-0.0988</v>
       </c>
       <c r="J94" t="n">
-        <v>-4.9242</v>
+        <v>-2.8652</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.93</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1698</v>
+        <v>-0.0988</v>
       </c>
       <c r="J95" t="n">
-        <v>-4.9242</v>
+        <v>-2.8652</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.84</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3212</v>
+        <v>-0.1969</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.3148</v>
+        <v>-5.7101</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.44</v>
       </c>
       <c r="I97" t="n">
-        <v>1.1151</v>
+        <v>1.071</v>
       </c>
       <c r="J97" t="n">
-        <v>32.3379</v>
+        <v>31.059</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.37</v>
       </c>
       <c r="I98" t="n">
-        <v>0.9665</v>
+        <v>0.959</v>
       </c>
       <c r="J98" t="n">
-        <v>28.0285</v>
+        <v>27.811</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.03</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0274</v>
+        <v>0.092</v>
       </c>
       <c r="J99" t="n">
-        <v>0.7946</v>
+        <v>2.668</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.01</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.0529</v>
+        <v>0.0139</v>
       </c>
       <c r="J100" t="n">
-        <v>-1.5341</v>
+        <v>0.4031</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1117</v>
+        <v>-0.041</v>
       </c>
       <c r="J101" t="n">
-        <v>-3.2393</v>
+        <v>-1.189</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.17</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4062</v>
+        <v>0.457</v>
       </c>
       <c r="J102" t="n">
-        <v>10.5612</v>
+        <v>11.882</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.07</v>
       </c>
       <c r="I103" t="n">
-        <v>0.245</v>
+        <v>0.2436</v>
       </c>
       <c r="J103" t="n">
-        <v>6.37</v>
+        <v>6.3336</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.83</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2584</v>
+        <v>-0.1889</v>
       </c>
       <c r="J104" t="n">
-        <v>-6.7184</v>
+        <v>-4.9114</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.66</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.5332</v>
+        <v>-0.3516</v>
       </c>
       <c r="J105" t="n">
-        <v>-13.8632</v>
+        <v>-9.1416</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.38</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.8801</v>
+        <v>-0.6094000000000001</v>
       </c>
       <c r="J106" t="n">
-        <v>-22.8826</v>
+        <v>-15.8444</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.68</v>
       </c>
       <c r="I107" t="n">
-        <v>1.5031</v>
+        <v>1.3317</v>
       </c>
       <c r="J107" t="n">
-        <v>39.0806</v>
+        <v>34.6242</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.45</v>
       </c>
       <c r="I108" t="n">
-        <v>1.0509</v>
+        <v>1.051</v>
       </c>
       <c r="J108" t="n">
-        <v>27.3234</v>
+        <v>27.326</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.36</v>
       </c>
       <c r="I109" t="n">
-        <v>0.8469</v>
+        <v>0.896</v>
       </c>
       <c r="J109" t="n">
-        <v>22.0194</v>
+        <v>23.296</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.25</v>
       </c>
       <c r="I110" t="n">
-        <v>0.5611</v>
+        <v>0.6534</v>
       </c>
       <c r="J110" t="n">
-        <v>14.5886</v>
+        <v>16.9884</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.95</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3674</v>
+        <v>-0.283</v>
       </c>
       <c r="J111" t="n">
-        <v>-9.5524</v>
+        <v>-7.358</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.11</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3011</v>
+        <v>0.3182</v>
       </c>
       <c r="J112" t="n">
-        <v>7.5275</v>
+        <v>7.955</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.04</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1758</v>
+        <v>0.1589</v>
       </c>
       <c r="J113" t="n">
-        <v>4.395</v>
+        <v>3.9725</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.0725</v>
       </c>
       <c r="J114" t="n">
-        <v>-1.775</v>
+        <v>-1.8125</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.63</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.581</v>
+        <v>-0.3839</v>
       </c>
       <c r="J115" t="n">
-        <v>-14.525</v>
+        <v>-9.5975</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.54</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6951000000000001</v>
+        <v>-0.4673</v>
       </c>
       <c r="J116" t="n">
-        <v>-17.3775</v>
+        <v>-11.6825</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.41</v>
       </c>
       <c r="I117" t="n">
-        <v>1.0266</v>
+        <v>1.0164</v>
       </c>
       <c r="J117" t="n">
-        <v>25.665</v>
+        <v>25.41</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.39</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9836</v>
+        <v>0.9825</v>
       </c>
       <c r="J118" t="n">
-        <v>24.59</v>
+        <v>24.5625</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.21</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5326</v>
+        <v>0.5812</v>
       </c>
       <c r="J119" t="n">
-        <v>13.315</v>
+        <v>14.53</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.17</v>
       </c>
       <c r="I120" t="n">
-        <v>0.4207</v>
+        <v>0.4838</v>
       </c>
       <c r="J120" t="n">
-        <v>10.5175</v>
+        <v>12.095</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.92</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4257</v>
+        <v>-0.3494</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.6425</v>
+        <v>-8.734999999999999</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>0.47</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.5273</v>
+        <v>-0.4288</v>
       </c>
       <c r="J122" t="n">
-        <v>-8.9641</v>
+        <v>-7.2896</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.45</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.5602</v>
+        <v>-0.4514</v>
       </c>
       <c r="J123" t="n">
-        <v>-9.523400000000001</v>
+        <v>-7.6738</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.37</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.7076</v>
+        <v>-0.5346</v>
       </c>
       <c r="J124" t="n">
-        <v>-12.0292</v>
+        <v>-9.088200000000001</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.27</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.906</v>
+        <v>-0.6342</v>
       </c>
       <c r="J125" t="n">
-        <v>-15.402</v>
+        <v>-10.7814</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.25</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.9374</v>
+        <v>-0.656</v>
       </c>
       <c r="J126" t="n">
-        <v>-15.9358</v>
+        <v>-11.152</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>2.46</v>
       </c>
       <c r="I127" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J127" t="n">
-        <v>35.0081</v>
+        <v>31.1746</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.87</v>
       </c>
       <c r="I128" t="n">
-        <v>1.639</v>
+        <v>1.4737</v>
       </c>
       <c r="J128" t="n">
-        <v>27.863</v>
+        <v>25.0529</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.83</v>
       </c>
       <c r="I129" t="n">
-        <v>1.5538</v>
+        <v>1.4325</v>
       </c>
       <c r="J129" t="n">
-        <v>26.4146</v>
+        <v>24.3525</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.74</v>
       </c>
       <c r="I130" t="n">
-        <v>1.3728</v>
+        <v>1.3372</v>
       </c>
       <c r="J130" t="n">
-        <v>23.3376</v>
+        <v>22.7324</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1.25</v>
       </c>
       <c r="I131" t="n">
-        <v>0.4284</v>
+        <v>0.5608</v>
       </c>
       <c r="J131" t="n">
-        <v>7.2828</v>
+        <v>9.5336</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.28</v>
       </c>
       <c r="I132" t="n">
-        <v>0.4926</v>
+        <v>0.5807</v>
       </c>
       <c r="J132" t="n">
-        <v>14.2854</v>
+        <v>16.8403</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.19</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3677</v>
+        <v>0.419</v>
       </c>
       <c r="J133" t="n">
-        <v>10.6633</v>
+        <v>12.151</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.98</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.0702</v>
+        <v>-0.0363</v>
       </c>
       <c r="J134" t="n">
-        <v>-2.0358</v>
+        <v>-1.0527</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.83</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3405</v>
+        <v>-0.2091</v>
       </c>
       <c r="J135" t="n">
-        <v>-9.874499999999999</v>
+        <v>-6.0639</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.74</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.468</v>
+        <v>-0.2984</v>
       </c>
       <c r="J136" t="n">
-        <v>-13.572</v>
+        <v>-8.653600000000001</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.61</v>
       </c>
       <c r="I137" t="n">
-        <v>1.4641</v>
+        <v>1.2977</v>
       </c>
       <c r="J137" t="n">
-        <v>42.4589</v>
+        <v>37.6333</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.17</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4951</v>
+        <v>0.4965</v>
       </c>
       <c r="J138" t="n">
-        <v>14.3579</v>
+        <v>14.3985</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.16</v>
       </c>
       <c r="I139" t="n">
-        <v>0.4654</v>
+        <v>0.4715</v>
       </c>
       <c r="J139" t="n">
-        <v>13.4966</v>
+        <v>13.6735</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.08</v>
       </c>
       <c r="I140" t="n">
-        <v>0.2064</v>
+        <v>0.2581</v>
       </c>
       <c r="J140" t="n">
-        <v>5.9856</v>
+        <v>7.4849</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.7</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.9435</v>
+        <v>-0.9118000000000001</v>
       </c>
       <c r="J141" t="n">
-        <v>-27.3615</v>
+        <v>-26.4422</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.25</v>
       </c>
       <c r="I142" t="n">
-        <v>0.7169</v>
+        <v>0.6985</v>
       </c>
       <c r="J142" t="n">
-        <v>19.3563</v>
+        <v>18.8595</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.15</v>
       </c>
       <c r="I143" t="n">
-        <v>0.4532</v>
+        <v>0.45</v>
       </c>
       <c r="J143" t="n">
-        <v>12.2364</v>
+        <v>12.15</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.13</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3901</v>
+        <v>0.3986</v>
       </c>
       <c r="J144" t="n">
-        <v>10.5327</v>
+        <v>10.7622</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.12</v>
       </c>
       <c r="I145" t="n">
-        <v>0.3496</v>
+        <v>0.373</v>
       </c>
       <c r="J145" t="n">
-        <v>9.4392</v>
+        <v>10.071</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.97</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2317</v>
+        <v>-0.1623</v>
       </c>
       <c r="J146" t="n">
-        <v>-6.2559</v>
+        <v>-4.3821</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.27</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4868</v>
+        <v>0.5714</v>
       </c>
       <c r="J147" t="n">
-        <v>13.1436</v>
+        <v>15.4278</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.23</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4323</v>
+        <v>0.4996</v>
       </c>
       <c r="J148" t="n">
-        <v>11.6721</v>
+        <v>13.4892</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.05</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1433</v>
+        <v>0.1431</v>
       </c>
       <c r="J149" t="n">
-        <v>3.8691</v>
+        <v>3.8637</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.75</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4499</v>
+        <v>-0.2862</v>
       </c>
       <c r="J150" t="n">
-        <v>-12.1473</v>
+        <v>-7.7274</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.61</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.631</v>
+        <v>-0.4182</v>
       </c>
       <c r="J151" t="n">
-        <v>-17.037</v>
+        <v>-11.2914</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>2.05</v>
       </c>
       <c r="I152" t="n">
-        <v>2.0053</v>
+        <v>1.7142</v>
       </c>
       <c r="J152" t="n">
-        <v>42.1113</v>
+        <v>35.9982</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.55</v>
       </c>
       <c r="I153" t="n">
-        <v>1.1644</v>
+        <v>1.15</v>
       </c>
       <c r="J153" t="n">
-        <v>24.4524</v>
+        <v>24.15</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.4</v>
       </c>
       <c r="I154" t="n">
-        <v>0.821</v>
+        <v>0.9495</v>
       </c>
       <c r="J154" t="n">
-        <v>17.241</v>
+        <v>19.9395</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.38</v>
       </c>
       <c r="I155" t="n">
-        <v>0.7784</v>
+        <v>0.9093</v>
       </c>
       <c r="J155" t="n">
-        <v>16.3464</v>
+        <v>19.0953</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.21</v>
       </c>
       <c r="I156" t="n">
-        <v>0.4047</v>
+        <v>0.5203</v>
       </c>
       <c r="J156" t="n">
-        <v>8.498699999999999</v>
+        <v>10.9263</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>0.97</v>
       </c>
       <c r="I157" t="n">
-        <v>0.0891</v>
+        <v>0.0534</v>
       </c>
       <c r="J157" t="n">
-        <v>1.8711</v>
+        <v>1.1214</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.73</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.3165</v>
+        <v>-0.2579</v>
       </c>
       <c r="J158" t="n">
-        <v>-6.6465</v>
+        <v>-5.4159</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.608</v>
+        <v>-0.4159</v>
       </c>
       <c r="J159" t="n">
-        <v>-12.768</v>
+        <v>-8.7339</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.54</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.6371</v>
+        <v>-0.4345</v>
       </c>
       <c r="J160" t="n">
-        <v>-13.3791</v>
+        <v>-9.124499999999999</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.39</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.837</v>
+        <v>-0.5760999999999999</v>
       </c>
       <c r="J161" t="n">
-        <v>-17.577</v>
+        <v>-12.0981</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I162" t="n">
-        <v>-0.2026</v>
+        <v>-0.1795</v>
       </c>
       <c r="J162" t="n">
-        <v>-4.052</v>
+        <v>-3.59</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.72</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.3452</v>
+        <v>-0.2728</v>
       </c>
       <c r="J163" t="n">
-        <v>-6.904</v>
+        <v>-5.456</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.67</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.4304</v>
+        <v>-0.3199</v>
       </c>
       <c r="J164" t="n">
-        <v>-8.608000000000001</v>
+        <v>-6.398</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.67</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.4304</v>
+        <v>-0.3199</v>
       </c>
       <c r="J165" t="n">
-        <v>-8.608000000000001</v>
+        <v>-6.398</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.43</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.7917</v>
+        <v>-0.5419</v>
       </c>
       <c r="J166" t="n">
-        <v>-15.834</v>
+        <v>-10.838</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.62</v>
       </c>
       <c r="I167" t="n">
-        <v>1.3397</v>
+        <v>1.2395</v>
       </c>
       <c r="J167" t="n">
-        <v>26.794</v>
+        <v>24.79</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.5</v>
       </c>
       <c r="I168" t="n">
-        <v>1.0956</v>
+        <v>1.0979</v>
       </c>
       <c r="J168" t="n">
-        <v>21.912</v>
+        <v>21.958</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.44</v>
       </c>
       <c r="I169" t="n">
-        <v>0.945</v>
+        <v>1.0244</v>
       </c>
       <c r="J169" t="n">
-        <v>18.9</v>
+        <v>20.488</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.41</v>
       </c>
       <c r="I170" t="n">
-        <v>0.8741</v>
+        <v>0.9777</v>
       </c>
       <c r="J170" t="n">
-        <v>17.482</v>
+        <v>19.554</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.29</v>
       </c>
       <c r="I171" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.7229</v>
       </c>
       <c r="J171" t="n">
-        <v>12.128</v>
+        <v>14.458</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.61</v>
       </c>
       <c r="I172" t="n">
-        <v>1.4461</v>
+        <v>1.2865</v>
       </c>
       <c r="J172" t="n">
-        <v>43.383</v>
+        <v>38.595</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.21</v>
       </c>
       <c r="I173" t="n">
-        <v>0.5787</v>
+        <v>0.587</v>
       </c>
       <c r="J173" t="n">
-        <v>17.361</v>
+        <v>17.61</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.14</v>
       </c>
       <c r="I174" t="n">
-        <v>0.3626</v>
+        <v>0.4153</v>
       </c>
       <c r="J174" t="n">
-        <v>10.878</v>
+        <v>12.459</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.04</v>
       </c>
       <c r="I175" t="n">
-        <v>0.0585</v>
+        <v>0.1242</v>
       </c>
       <c r="J175" t="n">
-        <v>1.755</v>
+        <v>3.726</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.9</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4701</v>
+        <v>-0.3984</v>
       </c>
       <c r="J176" t="n">
-        <v>-14.103</v>
+        <v>-11.952</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.08</v>
       </c>
       <c r="I177" t="n">
-        <v>0.2372</v>
+        <v>0.2393</v>
       </c>
       <c r="J177" t="n">
-        <v>7.116</v>
+        <v>7.179</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.07</v>
       </c>
       <c r="I178" t="n">
-        <v>0.2194</v>
+        <v>0.217</v>
       </c>
       <c r="J178" t="n">
-        <v>6.582</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.0775</v>
       </c>
       <c r="J179" t="n">
-        <v>-2.607</v>
+        <v>-2.325</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.82</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3192</v>
+        <v>-0.2051</v>
       </c>
       <c r="J180" t="n">
-        <v>-9.576000000000001</v>
+        <v>-6.153</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.52</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.7252</v>
+        <v>-0.4897</v>
       </c>
       <c r="J181" t="n">
-        <v>-21.756</v>
+        <v>-14.691</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.54</v>
       </c>
       <c r="I182" t="n">
-        <v>1.2243</v>
+        <v>1.1583</v>
       </c>
       <c r="J182" t="n">
-        <v>25.7103</v>
+        <v>24.3243</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.46</v>
       </c>
       <c r="I183" t="n">
-        <v>1.0596</v>
+        <v>1.0603</v>
       </c>
       <c r="J183" t="n">
-        <v>22.2516</v>
+        <v>22.2663</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.37</v>
       </c>
       <c r="I184" t="n">
-        <v>0.852</v>
+        <v>0.9133</v>
       </c>
       <c r="J184" t="n">
-        <v>17.892</v>
+        <v>19.1793</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.3</v>
       </c>
       <c r="I185" t="n">
-        <v>0.6685</v>
+        <v>0.7632</v>
       </c>
       <c r="J185" t="n">
-        <v>14.0385</v>
+        <v>16.0272</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.14</v>
       </c>
       <c r="I186" t="n">
-        <v>0.2804</v>
+        <v>0.3747</v>
       </c>
       <c r="J186" t="n">
-        <v>5.8884</v>
+        <v>7.8687</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.36</v>
       </c>
       <c r="I187" t="n">
-        <v>0.6931</v>
+        <v>0.873</v>
       </c>
       <c r="J187" t="n">
-        <v>14.5551</v>
+        <v>18.333</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2516</v>
+        <v>-0.2001</v>
       </c>
       <c r="J188" t="n">
-        <v>-5.2836</v>
+        <v>-4.2021</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.65</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.5252</v>
+        <v>-0.351</v>
       </c>
       <c r="J189" t="n">
-        <v>-11.0292</v>
+        <v>-7.371</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.62</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.5674</v>
+        <v>-0.3791</v>
       </c>
       <c r="J190" t="n">
-        <v>-11.9154</v>
+        <v>-7.9611</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.33</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.9288999999999999</v>
+        <v>-0.6476</v>
       </c>
       <c r="J191" t="n">
-        <v>-19.5069</v>
+        <v>-13.5996</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2572/event_2572_evp_summary.xlsx
+++ b/database/event/2572/event_2572_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.6868</v>
+        <v>4.7108</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7222</v>
+        <v>0.7259</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4778</v>
+        <v>1.5202</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6868</v>
+        <v>4.7108</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7618</v>
+        <v>2.6814</v>
       </c>
       <c r="G2" t="n">
-        <v>1.925</v>
+        <v>2.0294</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2446</v>
+        <v>3.9528</v>
       </c>
       <c r="I2" t="n">
-        <v>2.207</v>
+        <v>2.1345</v>
       </c>
       <c r="J2" t="n">
-        <v>1.925</v>
+        <v>2.0294</v>
       </c>
       <c r="K2" t="n">
         <v>50</v>
@@ -529,7 +529,7 @@
         <v>57</v>
       </c>
       <c r="M2" t="n">
-        <v>4.132</v>
+        <v>4.1639</v>
       </c>
       <c r="N2" t="n">
         <v>107</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.6412</v>
+        <v>3.6411</v>
       </c>
       <c r="C3" t="n">
         <v>0.5611</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0058</v>
+        <v>1.0333</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6412</v>
+        <v>3.6411</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6406</v>
+        <v>2.5627</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0006</v>
+        <v>1.0784</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8176</v>
+        <v>3.561</v>
       </c>
       <c r="I3" t="n">
-        <v>1.985</v>
+        <v>1.9229</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0006</v>
+        <v>1.0784</v>
       </c>
       <c r="K3" t="n">
         <v>57</v>
@@ -575,7 +575,7 @@
         <v>50</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9856</v>
+        <v>3.0013</v>
       </c>
       <c r="N3" t="n">
         <v>107</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.4831</v>
+        <v>3.4051</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5367</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9344</v>
+        <v>0.9258999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4831</v>
+        <v>3.4051</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1352</v>
+        <v>3.0593</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3479</v>
+        <v>0.3458</v>
       </c>
       <c r="H4" t="n">
-        <v>5.5603</v>
+        <v>5.1997</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8911</v>
+        <v>2.8078</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3479</v>
+        <v>0.3458</v>
       </c>
       <c r="K4" t="n">
         <v>115</v>
@@ -621,7 +621,7 @@
         <v>56</v>
       </c>
       <c r="M4" t="n">
-        <v>3.239</v>
+        <v>3.1536</v>
       </c>
       <c r="N4" t="n">
         <v>171</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.3777</v>
+        <v>3.2862</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5205</v>
+        <v>0.5064</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8868</v>
+        <v>0.8717</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3777</v>
+        <v>3.2862</v>
       </c>
       <c r="F5" t="n">
-        <v>3.4396</v>
+        <v>3.3664</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0619</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>6.6327</v>
+        <v>6.2129</v>
       </c>
       <c r="I5" t="n">
-        <v>3.4487</v>
+        <v>3.3549</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0619</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="K5" t="n">
         <v>99</v>
@@ -667,7 +667,7 @@
         <v>49</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3868</v>
+        <v>3.2747</v>
       </c>
       <c r="N5" t="n">
         <v>148</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.2231</v>
+        <v>3.2356</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4966</v>
+        <v>0.4986</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8171</v>
+        <v>0.8487</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2231</v>
+        <v>3.2356</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3464</v>
+        <v>2.2632</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8767</v>
+        <v>0.9724</v>
       </c>
       <c r="H6" t="n">
-        <v>2.781</v>
+        <v>2.5728</v>
       </c>
       <c r="I6" t="n">
-        <v>1.446</v>
+        <v>1.3893</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8767</v>
+        <v>0.9724</v>
       </c>
       <c r="K6" t="n">
         <v>50</v>
@@ -713,7 +713,7 @@
         <v>57</v>
       </c>
       <c r="M6" t="n">
-        <v>2.3227</v>
+        <v>2.3617</v>
       </c>
       <c r="N6" t="n">
         <v>107</v>
@@ -722,173 +722,173 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.1264</v>
+        <v>3.0904</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4817</v>
+        <v>0.4762</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7734</v>
+        <v>0.7826</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1264</v>
+        <v>3.0904</v>
       </c>
       <c r="F7" t="n">
-        <v>3.4651</v>
+        <v>1.7411</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3387</v>
+        <v>1.3493</v>
       </c>
       <c r="H7" t="n">
-        <v>6.7227</v>
+        <v>1.7411</v>
       </c>
       <c r="I7" t="n">
-        <v>3.4955</v>
+        <v>0.9402</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3387</v>
+        <v>1.3493</v>
       </c>
       <c r="K7" t="n">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="L7" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1568</v>
+        <v>2.2895</v>
       </c>
       <c r="N7" t="n">
-        <v>171</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.0545</v>
+        <v>3.0035</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4707</v>
+        <v>0.4628</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7409</v>
+        <v>0.7431</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0545</v>
+        <v>3.0035</v>
       </c>
       <c r="F8" t="n">
-        <v>3.443</v>
+        <v>1.0808</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3885</v>
+        <v>1.9227</v>
       </c>
       <c r="H8" t="n">
-        <v>6.6446</v>
+        <v>1.0808</v>
       </c>
       <c r="I8" t="n">
-        <v>3.4549</v>
+        <v>0.5836</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3885</v>
+        <v>1.9227</v>
       </c>
       <c r="K8" t="n">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="L8" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0664</v>
+        <v>2.5063</v>
       </c>
       <c r="N8" t="n">
-        <v>171</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0521</v>
+        <v>2.9918</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4703</v>
+        <v>0.461</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7399</v>
+        <v>0.7377</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0521</v>
+        <v>2.9918</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2159</v>
+        <v>3.3628</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1638</v>
+        <v>-0.371</v>
       </c>
       <c r="H9" t="n">
-        <v>5.8446</v>
+        <v>6.2008</v>
       </c>
       <c r="I9" t="n">
-        <v>3.0389</v>
+        <v>3.3484</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1638</v>
+        <v>-0.371</v>
       </c>
       <c r="K9" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="L9" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="M9" t="n">
-        <v>2.8751</v>
+        <v>2.9774</v>
       </c>
       <c r="N9" t="n">
-        <v>148</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0397</v>
+        <v>2.9815</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4684</v>
+        <v>0.4594</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7343</v>
+        <v>0.733</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0397</v>
+        <v>2.9815</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8463</v>
+        <v>1.4963</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1934</v>
+        <v>1.4852</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8463</v>
+        <v>1.4963</v>
       </c>
       <c r="I10" t="n">
-        <v>0.96</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1934</v>
+        <v>1.4852</v>
       </c>
       <c r="K10" t="n">
         <v>57</v>
@@ -897,7 +897,7 @@
         <v>50</v>
       </c>
       <c r="M10" t="n">
-        <v>2.1534</v>
+        <v>2.2932</v>
       </c>
       <c r="N10" t="n">
         <v>107</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0259</v>
+        <v>2.9743</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4663</v>
+        <v>0.4583</v>
       </c>
       <c r="D11" t="n">
-        <v>0.728</v>
+        <v>0.7298</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0259</v>
+        <v>2.9743</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5653</v>
+        <v>3.1311</v>
       </c>
       <c r="G11" t="n">
-        <v>1.4606</v>
+        <v>-0.1568</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5653</v>
+        <v>5.4364</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8139</v>
+        <v>2.9356</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4606</v>
+        <v>-0.1568</v>
       </c>
       <c r="K11" t="n">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="L11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M11" t="n">
-        <v>2.2745</v>
+        <v>2.7788</v>
       </c>
       <c r="N11" t="n">
-        <v>107</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9161</v>
+        <v>2.937</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4493</v>
+        <v>0.4526</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6785</v>
+        <v>0.7128</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9161</v>
+        <v>2.937</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1043</v>
+        <v>3.3574</v>
       </c>
       <c r="G12" t="n">
-        <v>1.8118</v>
+        <v>-0.4204</v>
       </c>
       <c r="H12" t="n">
-        <v>1.1043</v>
+        <v>6.1832</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5742</v>
+        <v>3.3389</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8118</v>
+        <v>-0.4204</v>
       </c>
       <c r="K12" t="n">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="L12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M12" t="n">
-        <v>2.386</v>
+        <v>2.9185</v>
       </c>
       <c r="N12" t="n">
-        <v>107</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7477</v>
+        <v>2.7313</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4234</v>
+        <v>0.4209</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6024</v>
+        <v>0.6191</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7477</v>
+        <v>2.7313</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8019</v>
+        <v>2.7992</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0542</v>
+        <v>-0.0679</v>
       </c>
       <c r="H13" t="n">
-        <v>4.386</v>
+        <v>4.3414</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2805</v>
+        <v>2.3443</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.0542</v>
+        <v>-0.0679</v>
       </c>
       <c r="K13" t="n">
         <v>115</v>
@@ -1035,7 +1035,7 @@
         <v>56</v>
       </c>
       <c r="M13" t="n">
-        <v>2.2263</v>
+        <v>2.2764</v>
       </c>
       <c r="N13" t="n">
         <v>171</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6752</v>
+        <v>2.7298</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4122</v>
+        <v>0.4206</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5697</v>
+        <v>0.6185</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6752</v>
+        <v>2.7298</v>
       </c>
       <c r="F14" t="n">
-        <v>2.709</v>
+        <v>2.7098</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0338</v>
+        <v>0.02</v>
       </c>
       <c r="H14" t="n">
-        <v>4.0586</v>
+        <v>4.0464</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1103</v>
+        <v>2.185</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0338</v>
+        <v>0.02</v>
       </c>
       <c r="K14" t="n">
         <v>50</v>
@@ -1081,7 +1081,7 @@
         <v>57</v>
       </c>
       <c r="M14" t="n">
-        <v>2.0765</v>
+        <v>2.205</v>
       </c>
       <c r="N14" t="n">
         <v>107</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.6005</v>
+        <v>2.5944</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4007</v>
+        <v>0.3998</v>
       </c>
       <c r="D15" t="n">
-        <v>0.536</v>
+        <v>0.5568</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6005</v>
+        <v>2.5944</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3257</v>
+        <v>2.2635</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2748</v>
+        <v>0.3309</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7081</v>
+        <v>2.5739</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4081</v>
+        <v>1.3899</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2748</v>
+        <v>0.3309</v>
       </c>
       <c r="K15" t="n">
         <v>50</v>
@@ -1127,7 +1127,7 @@
         <v>57</v>
       </c>
       <c r="M15" t="n">
-        <v>1.6829</v>
+        <v>1.7208</v>
       </c>
       <c r="N15" t="n">
         <v>107</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.5428</v>
+        <v>2.4413</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3918</v>
+        <v>0.3762</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5099</v>
+        <v>0.4871</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5428</v>
+        <v>2.4413</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6069</v>
+        <v>2.5311</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0641</v>
+        <v>-0.0898</v>
       </c>
       <c r="H16" t="n">
-        <v>3.6988</v>
+        <v>3.4567</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9232</v>
+        <v>1.8666</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0641</v>
+        <v>-0.0898</v>
       </c>
       <c r="K16" t="n">
         <v>99</v>
@@ -1173,7 +1173,7 @@
         <v>49</v>
       </c>
       <c r="M16" t="n">
-        <v>1.8591</v>
+        <v>1.7768</v>
       </c>
       <c r="N16" t="n">
         <v>148</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.4782</v>
+        <v>2.3534</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3819</v>
+        <v>0.3626</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4808</v>
+        <v>0.4471</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4782</v>
+        <v>2.3534</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7927</v>
+        <v>2.7024</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3145</v>
+        <v>-0.349</v>
       </c>
       <c r="H17" t="n">
-        <v>4.3535</v>
+        <v>4.0221</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2636</v>
+        <v>2.1719</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3145</v>
+        <v>-0.349</v>
       </c>
       <c r="K17" t="n">
         <v>99</v>
@@ -1219,7 +1219,7 @@
         <v>49</v>
       </c>
       <c r="M17" t="n">
-        <v>1.9491</v>
+        <v>1.8229</v>
       </c>
       <c r="N17" t="n">
         <v>148</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.4035</v>
+        <v>2.3127</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3704</v>
+        <v>0.3564</v>
       </c>
       <c r="D18" t="n">
-        <v>0.447</v>
+        <v>0.4286</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4035</v>
+        <v>2.3127</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4035</v>
+        <v>2.3127</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.4035</v>
+        <v>2.3369</v>
       </c>
       <c r="I18" t="n">
-        <v>2.4035</v>
+        <v>2.3369</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.4035</v>
+        <v>2.3369</v>
       </c>
       <c r="N18" t="n">
         <v>100</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.6107</v>
+        <v>1.4682</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2482</v>
+        <v>0.2262</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0891</v>
+        <v>0.0442</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6107</v>
+        <v>1.4682</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6107</v>
+        <v>1.4682</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6107</v>
+        <v>1.4682</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6107</v>
+        <v>1.4682</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.6107</v>
+        <v>1.4682</v>
       </c>
       <c r="N19" t="n">
         <v>125</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>yel</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4695</v>
+        <v>1.4191</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2264</v>
+        <v>0.2187</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0254</v>
+        <v>0.0218</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4695</v>
+        <v>1.4191</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4695</v>
+        <v>-0.9896</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2.4087</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4695</v>
+        <v>-0.9896</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4695</v>
+        <v>-0.5344</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>2.4087</v>
       </c>
       <c r="K20" t="n">
-        <v>125</v>
+        <v>57</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4695</v>
+        <v>1.8743</v>
       </c>
       <c r="N20" t="n">
-        <v>125</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>yel</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.2021</v>
+        <v>1.334</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1852</v>
+        <v>0.2056</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0953</v>
+        <v>-0.0169</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2021</v>
+        <v>1.334</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0784</v>
+        <v>1.334</v>
       </c>
       <c r="G21" t="n">
-        <v>2.2805</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0784</v>
+        <v>1.334</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5607</v>
+        <v>1.334</v>
       </c>
       <c r="J21" t="n">
-        <v>2.2805</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>57</v>
+        <v>125</v>
       </c>
       <c r="L21" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.7198</v>
+        <v>1.334</v>
       </c>
       <c r="N21" t="n">
-        <v>107</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22">
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.188</v>
+        <v>1.0313</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1831</v>
+        <v>0.1589</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1017</v>
+        <v>-0.1547</v>
       </c>
       <c r="E22" t="n">
-        <v>1.188</v>
+        <v>1.0313</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9602</v>
+        <v>1.8297</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7722</v>
+        <v>-0.7984</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9602</v>
+        <v>1.8297</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0192</v>
+        <v>0.988</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7722</v>
+        <v>-0.7984</v>
       </c>
       <c r="K22" t="n">
         <v>99</v>
@@ -1449,7 +1449,7 @@
         <v>49</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2470000000000001</v>
+        <v>0.1896</v>
       </c>
       <c r="N22" t="n">
         <v>148</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.0178</v>
+        <v>0.9291</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1568</v>
+        <v>0.1432</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1785</v>
+        <v>-0.2013</v>
       </c>
       <c r="E23" t="n">
-        <v>1.0178</v>
+        <v>0.9291</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0178</v>
+        <v>0.9291</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.0178</v>
+        <v>0.9291</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0178</v>
+        <v>0.9291</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.0178</v>
+        <v>0.9291</v>
       </c>
       <c r="N23" t="n">
         <v>76</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.976</v>
+        <v>0.8815</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1504</v>
+        <v>0.1358</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1974</v>
+        <v>-0.2229</v>
       </c>
       <c r="E24" t="n">
-        <v>0.976</v>
+        <v>0.8815</v>
       </c>
       <c r="F24" t="n">
-        <v>0.976</v>
+        <v>0.8815</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.976</v>
+        <v>0.8815</v>
       </c>
       <c r="I24" t="n">
-        <v>0.976</v>
+        <v>0.8815</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.976</v>
+        <v>0.8815</v>
       </c>
       <c r="N24" t="n">
         <v>100</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8511</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1311</v>
+        <v>0.1215</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2538</v>
+        <v>-0.2651</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8511</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8511</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8511</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8511</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.8511</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="N25" t="n">
         <v>100</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7174</v>
+        <v>0.6624</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1105</v>
+        <v>0.1021</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3141</v>
+        <v>-0.3227</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7174</v>
+        <v>0.6624</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7174</v>
+        <v>0.6624</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7174</v>
+        <v>0.6624</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7174</v>
+        <v>0.6624</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7174</v>
+        <v>0.6624</v>
       </c>
       <c r="N26" t="n">
         <v>100</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5877</v>
+        <v>0.5233</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0906</v>
+        <v>0.0806</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3727</v>
+        <v>-0.386</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5877</v>
+        <v>0.5233</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5877</v>
+        <v>0.5233</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5877</v>
+        <v>0.5233</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5877</v>
+        <v>0.5233</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.5877</v>
+        <v>0.5233</v>
       </c>
       <c r="N27" t="n">
         <v>100</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3753</v>
+        <v>0.3424</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0578</v>
+        <v>0.0528</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4686</v>
+        <v>-0.4683</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3753</v>
+        <v>0.3424</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3753</v>
+        <v>0.3424</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3753</v>
+        <v>0.3424</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3753</v>
+        <v>0.3424</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3753</v>
+        <v>0.3424</v>
       </c>
       <c r="N28" t="n">
         <v>76</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1035</v>
+        <v>0.033</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0159</v>
+        <v>0.0051</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5913</v>
+        <v>-0.6092</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1035</v>
+        <v>0.033</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1035</v>
+        <v>0.033</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1035</v>
+        <v>0.033</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1035</v>
+        <v>0.033</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1035</v>
+        <v>0.033</v>
       </c>
       <c r="N29" t="n">
         <v>125</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.1058</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0137</v>
+        <v>-0.0163</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6781</v>
+        <v>-0.6724</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.1058</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.1058</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.1058</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.1058</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.1058</v>
       </c>
       <c r="N30" t="n">
         <v>125</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2881</v>
+        <v>-0.3246</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0444</v>
+        <v>-0.05</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7681</v>
+        <v>-0.772</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2881</v>
+        <v>-0.3246</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.2881</v>
+        <v>-0.3246</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2881</v>
+        <v>-0.3246</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2881</v>
+        <v>-0.3246</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2881</v>
+        <v>-0.3246</v>
       </c>
       <c r="N31" t="n">
         <v>76</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3901</v>
+        <v>-0.4238</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0601</v>
+        <v>-0.0653</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8141</v>
+        <v>-0.8171</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3901</v>
+        <v>-0.4238</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3901</v>
+        <v>-0.4238</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3901</v>
+        <v>-0.4238</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3901</v>
+        <v>-0.4238</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3901</v>
+        <v>-0.4238</v>
       </c>
       <c r="N32" t="n">
         <v>72</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3935</v>
+        <v>-0.4242</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0606</v>
+        <v>-0.0654</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8157</v>
+        <v>-0.8173</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3935</v>
+        <v>-0.4242</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3935</v>
+        <v>-0.4242</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3935</v>
+        <v>-0.4242</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3935</v>
+        <v>-0.4242</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3935</v>
+        <v>-0.4242</v>
       </c>
       <c r="N33" t="n">
         <v>72</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4976</v>
+        <v>-0.543</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0767</v>
+        <v>-0.0837</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8627</v>
+        <v>-0.8714</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4976</v>
+        <v>-0.543</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4976</v>
+        <v>-0.543</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4976</v>
+        <v>-0.543</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4976</v>
+        <v>-0.543</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4976</v>
+        <v>-0.543</v>
       </c>
       <c r="N34" t="n">
         <v>72</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.5285</v>
+        <v>-0.5941</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0814</v>
+        <v>-0.0915</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8766</v>
+        <v>-0.8946</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5285</v>
+        <v>-0.5941</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.5285</v>
+        <v>-0.5941</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.5285</v>
+        <v>-0.5941</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5285</v>
+        <v>-0.5941</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5285</v>
+        <v>-0.5941</v>
       </c>
       <c r="N35" t="n">
         <v>125</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.5734</v>
+        <v>-0.6158</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.08840000000000001</v>
+        <v>-0.0949</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8969</v>
+        <v>-0.9045</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.5734</v>
+        <v>-0.6158</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.5734</v>
+        <v>-0.6158</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.5734</v>
+        <v>-0.6158</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5734</v>
+        <v>-0.6158</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.5734</v>
+        <v>-0.6158</v>
       </c>
       <c r="N36" t="n">
         <v>72</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.6387</v>
+        <v>-0.6853</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.0984</v>
+        <v>-0.1056</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9264</v>
+        <v>-0.9362</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.6387</v>
+        <v>-0.6853</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.6387</v>
+        <v>-0.6853</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.6387</v>
+        <v>-0.6853</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.6387</v>
+        <v>-0.6853</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.6387</v>
+        <v>-0.6853</v>
       </c>
       <c r="N37" t="n">
         <v>76</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0297</v>
+        <v>-0.7652</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1587</v>
+        <v>-0.1179</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1029</v>
+        <v>-0.9725</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0297</v>
+        <v>-0.7652</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.753</v>
+        <v>-0.5802</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.2767</v>
+        <v>-0.185</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.753</v>
+        <v>-0.5802</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3915</v>
+        <v>-0.3133</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.2767</v>
+        <v>-0.185</v>
       </c>
       <c r="K38" t="n">
         <v>50</v>
@@ -2185,7 +2185,7 @@
         <v>57</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.6682</v>
+        <v>-0.4983</v>
       </c>
       <c r="N38" t="n">
         <v>107</v>
@@ -2194,139 +2194,139 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Slemmy</t>
+          <t>FNS</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.4539</v>
+        <v>-1.3924</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.224</v>
+        <v>-0.2146</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2944</v>
+        <v>-1.2581</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.4539</v>
+        <v>-1.3924</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.4539</v>
+        <v>-0.9274</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.465</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.4539</v>
+        <v>-0.9274</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.4539</v>
+        <v>-0.5008</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.465</v>
       </c>
       <c r="K39" t="n">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.4539</v>
+        <v>-0.9658</v>
       </c>
       <c r="N39" t="n">
-        <v>76</v>
+        <v>171</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>tutehen</t>
+          <t>Slemmy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.4897</v>
+        <v>-1.467</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2295</v>
+        <v>-0.226</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3105</v>
+        <v>-1.292</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.4897</v>
+        <v>-1.467</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.4897</v>
+        <v>-1.467</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.4897</v>
+        <v>-1.467</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.4897</v>
+        <v>-1.467</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.4897</v>
+        <v>-1.467</v>
       </c>
       <c r="N40" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FNS</t>
+          <t>tutehen</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.5595</v>
+        <v>-1.4967</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2403</v>
+        <v>-0.2306</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3421</v>
+        <v>-1.3055</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.5595</v>
+        <v>-1.4967</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.0991</v>
+        <v>-1.4967</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.4604</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.0991</v>
+        <v>-1.4967</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5715</v>
+        <v>-1.4967</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.4604</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="L41" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.0319</v>
+        <v>-1.4967</v>
       </c>
       <c r="N41" t="n">
-        <v>171</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2429,10 +2429,10 @@
         <v>1.3</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6578000000000001</v>
+        <v>0.6274</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6578000000000001</v>
+        <v>0.6274</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.95</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0679</v>
+        <v>-0.08</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0679</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.85</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1772</v>
+        <v>-0.1932</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1772</v>
+        <v>-0.1932</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.78</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2477</v>
+        <v>-0.2633</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2477</v>
+        <v>-0.2633</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.66</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3631</v>
+        <v>-0.3756</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3631</v>
+        <v>-0.3756</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.47</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0875</v>
+        <v>1.0653</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0875</v>
+        <v>1.0653</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.36</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9093</v>
+        <v>0.8582</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9093</v>
+        <v>0.8582</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.33</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8435</v>
+        <v>0.8002</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8435</v>
+        <v>0.8002</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.18</v>
       </c>
       <c r="I10" t="n">
-        <v>0.498</v>
+        <v>0.4921</v>
       </c>
       <c r="J10" t="n">
-        <v>0.498</v>
+        <v>0.4921</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.02</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0298</v>
+        <v>0.0553</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0298</v>
+        <v>0.0553</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>2.1</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5334</v>
+        <v>1.6661</v>
       </c>
       <c r="J12" t="n">
-        <v>33.7348</v>
+        <v>36.6542</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.41</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7232</v>
+        <v>0.8069</v>
       </c>
       <c r="J13" t="n">
-        <v>15.9104</v>
+        <v>17.7518</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.22</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4752</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>10.4544</v>
+        <v>11.6996</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.11</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2896</v>
+        <v>0.3076</v>
       </c>
       <c r="J15" t="n">
-        <v>6.3712</v>
+        <v>6.7672</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.05</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1107</v>
+        <v>0.1404</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4354</v>
+        <v>3.0888</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0477</v>
+        <v>-0.0677</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.0494</v>
+        <v>-1.4894</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.89</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1093</v>
+        <v>-0.1305</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.4046</v>
+        <v>-2.871</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.197</v>
+        <v>-0.2178</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.334</v>
+        <v>-4.7916</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.58</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4137</v>
+        <v>-0.4281</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.1014</v>
+        <v>-9.418200000000001</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.46</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5255</v>
+        <v>-0.5332</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.561</v>
+        <v>-11.7304</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.62</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0242</v>
+        <v>1.123</v>
       </c>
       <c r="J22" t="n">
-        <v>27.6534</v>
+        <v>30.321</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.36</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6884</v>
+        <v>0.7622</v>
       </c>
       <c r="J23" t="n">
-        <v>18.5868</v>
+        <v>20.5794</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.18</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4406</v>
+        <v>0.4866</v>
       </c>
       <c r="J24" t="n">
-        <v>11.8962</v>
+        <v>13.1382</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.92</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3404</v>
+        <v>-0.3227</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.190799999999999</v>
+        <v>-8.712899999999999</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.84</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5661</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>-15.2847</v>
+        <v>-14.2749</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.16</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3617</v>
+        <v>0.3764</v>
       </c>
       <c r="J27" t="n">
-        <v>9.7659</v>
+        <v>10.1628</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.01</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0474</v>
+        <v>0.0503</v>
       </c>
       <c r="J28" t="n">
-        <v>1.2798</v>
+        <v>1.3581</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.99</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0164</v>
+        <v>-0.0221</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.4428</v>
+        <v>-0.5967</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1175</v>
+        <v>-0.1312</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.1725</v>
+        <v>-3.5424</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.67</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3585</v>
+        <v>-0.3703</v>
       </c>
       <c r="J31" t="n">
-        <v>-9.679500000000001</v>
+        <v>-9.998100000000001</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.32</v>
       </c>
       <c r="I32" t="n">
-        <v>0.659</v>
+        <v>0.7247</v>
       </c>
       <c r="J32" t="n">
-        <v>19.77</v>
+        <v>21.741</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.16</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4252</v>
+        <v>0.465</v>
       </c>
       <c r="J33" t="n">
-        <v>12.756</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.12</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3626</v>
+        <v>0.3779</v>
       </c>
       <c r="J34" t="n">
-        <v>10.878</v>
+        <v>11.337</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.98</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1119</v>
+        <v>-0.112</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.357</v>
+        <v>-3.36</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.79</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6685</v>
+        <v>-0.6254999999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>-20.055</v>
+        <v>-18.765</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.05</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1543</v>
+        <v>0.1587</v>
       </c>
       <c r="J37" t="n">
-        <v>4.629</v>
+        <v>4.761</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.04</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1304</v>
+        <v>0.135</v>
       </c>
       <c r="J38" t="n">
-        <v>3.912</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.01</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0498</v>
+        <v>0.052</v>
       </c>
       <c r="J39" t="n">
-        <v>1.494</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.82</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2115</v>
+        <v>-0.2266</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.345</v>
+        <v>-6.798</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.77</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2613</v>
+        <v>-0.276</v>
       </c>
       <c r="J41" t="n">
-        <v>-7.839</v>
+        <v>-8.279999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.52</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8772</v>
+        <v>0.9701</v>
       </c>
       <c r="J42" t="n">
-        <v>22.8072</v>
+        <v>25.2226</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.33</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6344</v>
+        <v>0.7062</v>
       </c>
       <c r="J43" t="n">
-        <v>16.4944</v>
+        <v>18.3612</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.31</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6082</v>
+        <v>0.6773</v>
       </c>
       <c r="J44" t="n">
-        <v>15.8132</v>
+        <v>17.6098</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.28</v>
       </c>
       <c r="I45" t="n">
-        <v>0.569</v>
+        <v>0.6337</v>
       </c>
       <c r="J45" t="n">
-        <v>14.794</v>
+        <v>16.4762</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.91</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3911</v>
+        <v>-0.365</v>
       </c>
       <c r="J46" t="n">
-        <v>-10.1686</v>
+        <v>-9.49</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.06</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2175</v>
+        <v>0.2108</v>
       </c>
       <c r="J47" t="n">
-        <v>5.655</v>
+        <v>5.4808</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.89</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1272</v>
+        <v>-0.1444</v>
       </c>
       <c r="J48" t="n">
-        <v>-3.3072</v>
+        <v>-3.7544</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.89</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1272</v>
+        <v>-0.1444</v>
       </c>
       <c r="J49" t="n">
-        <v>-3.3072</v>
+        <v>-3.7544</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2085</v>
+        <v>-0.2266</v>
       </c>
       <c r="J50" t="n">
-        <v>-5.421</v>
+        <v>-5.8916</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.49</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5102</v>
+        <v>-0.517</v>
       </c>
       <c r="J51" t="n">
-        <v>-13.2652</v>
+        <v>-13.442</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.71</v>
       </c>
       <c r="I52" t="n">
-        <v>1.4114</v>
+        <v>1.3901</v>
       </c>
       <c r="J52" t="n">
-        <v>39.5192</v>
+        <v>38.9228</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.14</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4153</v>
+        <v>0.4128</v>
       </c>
       <c r="J53" t="n">
-        <v>11.6284</v>
+        <v>11.5584</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.13</v>
       </c>
       <c r="I54" t="n">
-        <v>0.389</v>
+        <v>0.3888</v>
       </c>
       <c r="J54" t="n">
-        <v>10.892</v>
+        <v>10.8864</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.98</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1396</v>
+        <v>-0.1313</v>
       </c>
       <c r="J55" t="n">
-        <v>-3.9088</v>
+        <v>-3.6764</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2776</v>
+        <v>-0.2642</v>
       </c>
       <c r="J56" t="n">
-        <v>-7.7728</v>
+        <v>-7.3976</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.24</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5599</v>
+        <v>0.5365</v>
       </c>
       <c r="J57" t="n">
-        <v>15.6772</v>
+        <v>15.022</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.16</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4062</v>
+        <v>0.3951</v>
       </c>
       <c r="J58" t="n">
-        <v>11.3736</v>
+        <v>11.0628</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.88</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1439</v>
+        <v>-0.1599</v>
       </c>
       <c r="J59" t="n">
-        <v>-4.0292</v>
+        <v>-4.4772</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.6</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.416</v>
+        <v>-0.4268</v>
       </c>
       <c r="J60" t="n">
-        <v>-11.648</v>
+        <v>-11.9504</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.54</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4712</v>
+        <v>-0.4793</v>
       </c>
       <c r="J61" t="n">
-        <v>-13.1936</v>
+        <v>-13.4204</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.59</v>
       </c>
       <c r="I62" t="n">
-        <v>1.2029</v>
+        <v>1.1799</v>
       </c>
       <c r="J62" t="n">
-        <v>25.2609</v>
+        <v>24.7779</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.54</v>
       </c>
       <c r="I63" t="n">
-        <v>1.1441</v>
+        <v>1.1165</v>
       </c>
       <c r="J63" t="n">
-        <v>24.0261</v>
+        <v>23.4465</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.43</v>
       </c>
       <c r="I64" t="n">
-        <v>1.0089</v>
+        <v>0.9628</v>
       </c>
       <c r="J64" t="n">
-        <v>21.1869</v>
+        <v>20.2188</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.4</v>
       </c>
       <c r="I65" t="n">
-        <v>0.9584</v>
+        <v>0.9105</v>
       </c>
       <c r="J65" t="n">
-        <v>20.1264</v>
+        <v>19.1205</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.35</v>
       </c>
       <c r="I66" t="n">
-        <v>0.8551</v>
+        <v>0.8168</v>
       </c>
       <c r="J66" t="n">
-        <v>17.9571</v>
+        <v>17.1528</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>0.0012</v>
+        <v>-0.0295</v>
       </c>
       <c r="J67" t="n">
-        <v>0.0252</v>
+        <v>-0.6195000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.82</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.15</v>
+        <v>-0.1789</v>
       </c>
       <c r="J68" t="n">
-        <v>-3.15</v>
+        <v>-3.7569</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.66</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3195</v>
+        <v>-0.3418</v>
       </c>
       <c r="J69" t="n">
-        <v>-6.7095</v>
+        <v>-7.1778</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.48</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4846</v>
+        <v>-0.4983</v>
       </c>
       <c r="J70" t="n">
-        <v>-10.1766</v>
+        <v>-10.4643</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.12</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.8304</v>
+        <v>-0.8149</v>
       </c>
       <c r="J71" t="n">
-        <v>-17.4384</v>
+        <v>-17.1129</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.26</v>
       </c>
       <c r="I72" t="n">
-        <v>0.592</v>
+        <v>0.5666</v>
       </c>
       <c r="J72" t="n">
-        <v>15.984</v>
+        <v>15.2982</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.9</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.124</v>
+        <v>-0.1391</v>
       </c>
       <c r="J73" t="n">
-        <v>-3.348</v>
+        <v>-3.7557</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.82</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2061</v>
+        <v>-0.2225</v>
       </c>
       <c r="J74" t="n">
-        <v>-5.5647</v>
+        <v>-6.0075</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2161</v>
+        <v>-0.2325</v>
       </c>
       <c r="J75" t="n">
-        <v>-5.8347</v>
+        <v>-6.2775</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.68</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3424</v>
+        <v>-0.356</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.2448</v>
+        <v>-9.612</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.3</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8179</v>
+        <v>0.7699</v>
       </c>
       <c r="J77" t="n">
-        <v>22.0833</v>
+        <v>20.7873</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.21</v>
       </c>
       <c r="I78" t="n">
-        <v>0.6008</v>
+        <v>0.5782</v>
       </c>
       <c r="J78" t="n">
-        <v>16.2216</v>
+        <v>15.6114</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.15</v>
       </c>
       <c r="I79" t="n">
-        <v>0.45</v>
+        <v>0.4423</v>
       </c>
       <c r="J79" t="n">
-        <v>12.15</v>
+        <v>11.9421</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.12</v>
       </c>
       <c r="I80" t="n">
-        <v>0.373</v>
+        <v>0.3715</v>
       </c>
       <c r="J80" t="n">
-        <v>10.071</v>
+        <v>10.0305</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.84</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5507</v>
+        <v>-0.5178</v>
       </c>
       <c r="J81" t="n">
-        <v>-14.8689</v>
+        <v>-13.9806</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.3</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6226</v>
+        <v>0.6014</v>
       </c>
       <c r="J82" t="n">
-        <v>16.1876</v>
+        <v>15.6364</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.05</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1422</v>
+        <v>0.15</v>
       </c>
       <c r="J83" t="n">
-        <v>3.6972</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.99</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.0198</v>
+        <v>-0.0247</v>
       </c>
       <c r="J84" t="n">
-        <v>-0.5148</v>
+        <v>-0.6422</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.8</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2374</v>
+        <v>-0.2511</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.1724</v>
+        <v>-6.5286</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.79</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2474</v>
+        <v>-0.261</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.4324</v>
+        <v>-6.786</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.43</v>
       </c>
       <c r="I87" t="n">
-        <v>1.0567</v>
+        <v>1.007</v>
       </c>
       <c r="J87" t="n">
-        <v>27.4742</v>
+        <v>26.182</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.31</v>
       </c>
       <c r="I88" t="n">
-        <v>0.8243</v>
+        <v>0.7785</v>
       </c>
       <c r="J88" t="n">
-        <v>21.4318</v>
+        <v>20.241</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.28</v>
       </c>
       <c r="I89" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="J89" t="n">
-        <v>19.617</v>
+        <v>18.6472</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.08</v>
       </c>
       <c r="I90" t="n">
-        <v>0.251</v>
+        <v>0.261</v>
       </c>
       <c r="J90" t="n">
-        <v>6.526</v>
+        <v>6.786</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.77</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.7455000000000001</v>
+        <v>-0.6889</v>
       </c>
       <c r="J91" t="n">
-        <v>-19.383</v>
+        <v>-17.9114</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.2</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4426</v>
+        <v>0.4366</v>
       </c>
       <c r="J92" t="n">
-        <v>12.8354</v>
+        <v>12.6614</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.04</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1184</v>
+        <v>0.1263</v>
       </c>
       <c r="J93" t="n">
-        <v>3.4336</v>
+        <v>3.6627</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.93</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0988</v>
+        <v>-0.1105</v>
       </c>
       <c r="J94" t="n">
-        <v>-2.8652</v>
+        <v>-3.2045</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.93</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.0988</v>
+        <v>-0.1105</v>
       </c>
       <c r="J95" t="n">
-        <v>-2.8652</v>
+        <v>-3.2045</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.84</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1969</v>
+        <v>-0.2108</v>
       </c>
       <c r="J96" t="n">
-        <v>-5.7101</v>
+        <v>-6.1132</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.44</v>
       </c>
       <c r="I97" t="n">
-        <v>1.071</v>
+        <v>1.024</v>
       </c>
       <c r="J97" t="n">
-        <v>31.059</v>
+        <v>29.696</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.37</v>
       </c>
       <c r="I98" t="n">
-        <v>0.959</v>
+        <v>0.8993</v>
       </c>
       <c r="J98" t="n">
-        <v>27.811</v>
+        <v>26.0797</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.03</v>
       </c>
       <c r="I99" t="n">
-        <v>0.092</v>
+        <v>0.1094</v>
       </c>
       <c r="J99" t="n">
-        <v>2.668</v>
+        <v>3.1726</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.01</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0139</v>
+        <v>0.0315</v>
       </c>
       <c r="J100" t="n">
-        <v>0.4031</v>
+        <v>0.9135</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.041</v>
+        <v>-0.0283</v>
       </c>
       <c r="J101" t="n">
-        <v>-1.189</v>
+        <v>-0.8207</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.17</v>
       </c>
       <c r="I102" t="n">
-        <v>0.457</v>
+        <v>0.4363</v>
       </c>
       <c r="J102" t="n">
-        <v>11.882</v>
+        <v>11.3438</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.07</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2436</v>
+        <v>0.2355</v>
       </c>
       <c r="J103" t="n">
-        <v>6.3336</v>
+        <v>6.123</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.83</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1889</v>
+        <v>-0.207</v>
       </c>
       <c r="J104" t="n">
-        <v>-4.9114</v>
+        <v>-5.382</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.66</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3516</v>
+        <v>-0.3665</v>
       </c>
       <c r="J105" t="n">
-        <v>-9.1416</v>
+        <v>-9.529</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.38</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6094000000000001</v>
+        <v>-0.6099</v>
       </c>
       <c r="J106" t="n">
-        <v>-15.8444</v>
+        <v>-15.8574</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.68</v>
       </c>
       <c r="I107" t="n">
-        <v>1.3317</v>
+        <v>1.3132</v>
       </c>
       <c r="J107" t="n">
-        <v>34.6242</v>
+        <v>34.1432</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.45</v>
       </c>
       <c r="I108" t="n">
-        <v>1.051</v>
+        <v>1.0076</v>
       </c>
       <c r="J108" t="n">
-        <v>27.326</v>
+        <v>26.1976</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.36</v>
       </c>
       <c r="I109" t="n">
-        <v>0.896</v>
+        <v>0.8489</v>
       </c>
       <c r="J109" t="n">
-        <v>23.296</v>
+        <v>22.0714</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.25</v>
       </c>
       <c r="I110" t="n">
-        <v>0.6534</v>
+        <v>0.6341</v>
       </c>
       <c r="J110" t="n">
-        <v>16.9884</v>
+        <v>16.4866</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.95</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.283</v>
+        <v>-0.2601</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.358</v>
+        <v>-6.7626</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.11</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3182</v>
+        <v>0.3096</v>
       </c>
       <c r="J112" t="n">
-        <v>7.955</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.04</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1589</v>
+        <v>0.1557</v>
       </c>
       <c r="J113" t="n">
-        <v>3.9725</v>
+        <v>3.8925</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.0725</v>
+        <v>-0.0871</v>
       </c>
       <c r="J114" t="n">
-        <v>-1.8125</v>
+        <v>-2.1775</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.63</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3839</v>
+        <v>-0.3968</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.5975</v>
+        <v>-9.92</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.54</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4673</v>
+        <v>-0.4762</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.6825</v>
+        <v>-11.905</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.41</v>
       </c>
       <c r="I117" t="n">
-        <v>1.0164</v>
+        <v>0.9623</v>
       </c>
       <c r="J117" t="n">
-        <v>25.41</v>
+        <v>24.0575</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.39</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9825</v>
+        <v>0.9258</v>
       </c>
       <c r="J118" t="n">
-        <v>24.5625</v>
+        <v>23.145</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.21</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5812</v>
+        <v>0.5648</v>
       </c>
       <c r="J119" t="n">
-        <v>14.53</v>
+        <v>14.12</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.17</v>
       </c>
       <c r="I120" t="n">
-        <v>0.4838</v>
+        <v>0.4769</v>
       </c>
       <c r="J120" t="n">
-        <v>12.095</v>
+        <v>11.9225</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.92</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3494</v>
+        <v>-0.329</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.734999999999999</v>
+        <v>-8.225</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>0.47</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.4288</v>
+        <v>-0.4565</v>
       </c>
       <c r="J122" t="n">
-        <v>-7.2896</v>
+        <v>-7.7605</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.45</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.4514</v>
+        <v>-0.477</v>
       </c>
       <c r="J123" t="n">
-        <v>-7.6738</v>
+        <v>-8.109</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.37</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.5346</v>
+        <v>-0.5526</v>
       </c>
       <c r="J124" t="n">
-        <v>-9.088200000000001</v>
+        <v>-9.3942</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.27</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.6342</v>
+        <v>-0.6429</v>
       </c>
       <c r="J125" t="n">
-        <v>-10.7814</v>
+        <v>-10.9293</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.25</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.656</v>
+        <v>-0.6624</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.152</v>
+        <v>-11.2608</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>2.46</v>
       </c>
       <c r="I127" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J127" t="n">
-        <v>31.1746</v>
+        <v>32.9324</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.87</v>
       </c>
       <c r="I128" t="n">
-        <v>1.4737</v>
+        <v>1.4774</v>
       </c>
       <c r="J128" t="n">
-        <v>25.0529</v>
+        <v>25.1158</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.83</v>
       </c>
       <c r="I129" t="n">
-        <v>1.4325</v>
+        <v>1.4333</v>
       </c>
       <c r="J129" t="n">
-        <v>24.3525</v>
+        <v>24.3661</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.74</v>
       </c>
       <c r="I130" t="n">
-        <v>1.3372</v>
+        <v>1.3314</v>
       </c>
       <c r="J130" t="n">
-        <v>22.7324</v>
+        <v>22.6338</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1.25</v>
       </c>
       <c r="I131" t="n">
-        <v>0.5608</v>
+        <v>0.5693</v>
       </c>
       <c r="J131" t="n">
-        <v>9.5336</v>
+        <v>9.678100000000001</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.28</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5807</v>
+        <v>0.5645</v>
       </c>
       <c r="J132" t="n">
-        <v>16.8403</v>
+        <v>16.3705</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.19</v>
       </c>
       <c r="I133" t="n">
-        <v>0.419</v>
+        <v>0.4157</v>
       </c>
       <c r="J133" t="n">
-        <v>12.151</v>
+        <v>12.0553</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.98</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.0363</v>
+        <v>-0.043</v>
       </c>
       <c r="J134" t="n">
-        <v>-1.0527</v>
+        <v>-1.247</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.83</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2091</v>
+        <v>-0.2226</v>
       </c>
       <c r="J135" t="n">
-        <v>-6.0639</v>
+        <v>-6.4554</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.74</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2984</v>
+        <v>-0.3108</v>
       </c>
       <c r="J136" t="n">
-        <v>-8.653600000000001</v>
+        <v>-9.013199999999999</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.61</v>
       </c>
       <c r="I137" t="n">
-        <v>1.2977</v>
+        <v>1.268</v>
       </c>
       <c r="J137" t="n">
-        <v>37.6333</v>
+        <v>36.772</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.17</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4965</v>
+        <v>0.4855</v>
       </c>
       <c r="J138" t="n">
-        <v>14.3985</v>
+        <v>14.0795</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.16</v>
       </c>
       <c r="I139" t="n">
-        <v>0.4715</v>
+        <v>0.4627</v>
       </c>
       <c r="J139" t="n">
-        <v>13.6735</v>
+        <v>13.4183</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.08</v>
       </c>
       <c r="I140" t="n">
-        <v>0.2581</v>
+        <v>0.2658</v>
       </c>
       <c r="J140" t="n">
-        <v>7.4849</v>
+        <v>7.7082</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.7</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.9118000000000001</v>
+        <v>-0.8359</v>
       </c>
       <c r="J141" t="n">
-        <v>-26.4422</v>
+        <v>-24.2411</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.25</v>
       </c>
       <c r="I142" t="n">
-        <v>0.6985</v>
+        <v>0.6649</v>
       </c>
       <c r="J142" t="n">
-        <v>18.8595</v>
+        <v>17.9523</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.15</v>
       </c>
       <c r="I143" t="n">
-        <v>0.45</v>
+        <v>0.4423</v>
       </c>
       <c r="J143" t="n">
-        <v>12.15</v>
+        <v>11.9421</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.13</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3986</v>
+        <v>0.3952</v>
       </c>
       <c r="J144" t="n">
-        <v>10.7622</v>
+        <v>10.6704</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.12</v>
       </c>
       <c r="I145" t="n">
-        <v>0.373</v>
+        <v>0.3715</v>
       </c>
       <c r="J145" t="n">
-        <v>10.071</v>
+        <v>10.0305</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.97</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1623</v>
+        <v>-0.1578</v>
       </c>
       <c r="J146" t="n">
-        <v>-4.3821</v>
+        <v>-4.2606</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.27</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5714</v>
+        <v>0.5545</v>
       </c>
       <c r="J147" t="n">
-        <v>15.4278</v>
+        <v>14.9715</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.23</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4996</v>
+        <v>0.4888</v>
       </c>
       <c r="J148" t="n">
-        <v>13.4892</v>
+        <v>13.1976</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.05</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1431</v>
+        <v>0.1506</v>
       </c>
       <c r="J149" t="n">
-        <v>3.8637</v>
+        <v>4.0662</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.75</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2862</v>
+        <v>-0.2993</v>
       </c>
       <c r="J150" t="n">
-        <v>-7.7274</v>
+        <v>-8.081099999999999</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.61</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4182</v>
+        <v>-0.4269</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.2914</v>
+        <v>-11.5263</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>2.05</v>
       </c>
       <c r="I152" t="n">
-        <v>1.7142</v>
+        <v>1.7223</v>
       </c>
       <c r="J152" t="n">
-        <v>35.9982</v>
+        <v>36.1683</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.55</v>
       </c>
       <c r="I153" t="n">
-        <v>1.15</v>
+        <v>1.1241</v>
       </c>
       <c r="J153" t="n">
-        <v>24.15</v>
+        <v>23.6061</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.4</v>
       </c>
       <c r="I154" t="n">
-        <v>0.9495</v>
+        <v>0.9038</v>
       </c>
       <c r="J154" t="n">
-        <v>19.9395</v>
+        <v>18.9798</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.38</v>
       </c>
       <c r="I155" t="n">
-        <v>0.9093</v>
+        <v>0.8665</v>
       </c>
       <c r="J155" t="n">
-        <v>19.0953</v>
+        <v>18.1965</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.21</v>
       </c>
       <c r="I156" t="n">
-        <v>0.5203</v>
+        <v>0.5226</v>
       </c>
       <c r="J156" t="n">
-        <v>10.9263</v>
+        <v>10.9746</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>0.97</v>
       </c>
       <c r="I157" t="n">
-        <v>0.0534</v>
+        <v>0.0064</v>
       </c>
       <c r="J157" t="n">
-        <v>1.1214</v>
+        <v>0.1344</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.73</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.2579</v>
+        <v>-0.2814</v>
       </c>
       <c r="J158" t="n">
-        <v>-5.4159</v>
+        <v>-5.9094</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.4159</v>
+        <v>-0.4329</v>
       </c>
       <c r="J159" t="n">
-        <v>-8.7339</v>
+        <v>-9.0909</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.54</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4345</v>
+        <v>-0.4505</v>
       </c>
       <c r="J160" t="n">
-        <v>-9.124499999999999</v>
+        <v>-9.4605</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.39</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5760999999999999</v>
+        <v>-0.5823</v>
       </c>
       <c r="J161" t="n">
-        <v>-12.0981</v>
+        <v>-12.2283</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I162" t="n">
-        <v>-0.1795</v>
+        <v>-0.2042</v>
       </c>
       <c r="J162" t="n">
-        <v>-3.59</v>
+        <v>-4.084</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.72</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.2728</v>
+        <v>-0.2948</v>
       </c>
       <c r="J163" t="n">
-        <v>-5.456</v>
+        <v>-5.896</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.67</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.3199</v>
+        <v>-0.3403</v>
       </c>
       <c r="J164" t="n">
-        <v>-6.398</v>
+        <v>-6.806</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.67</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3199</v>
+        <v>-0.3403</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.398</v>
+        <v>-6.806</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.43</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5419</v>
+        <v>-0.5501</v>
       </c>
       <c r="J166" t="n">
-        <v>-10.838</v>
+        <v>-11.002</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.62</v>
       </c>
       <c r="I167" t="n">
-        <v>1.2395</v>
+        <v>1.2189</v>
       </c>
       <c r="J167" t="n">
-        <v>24.79</v>
+        <v>24.378</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.5</v>
       </c>
       <c r="I168" t="n">
-        <v>1.0979</v>
+        <v>1.0658</v>
       </c>
       <c r="J168" t="n">
-        <v>21.958</v>
+        <v>21.316</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.44</v>
       </c>
       <c r="I169" t="n">
-        <v>1.0244</v>
+        <v>0.9798</v>
       </c>
       <c r="J169" t="n">
-        <v>20.488</v>
+        <v>19.596</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.41</v>
       </c>
       <c r="I170" t="n">
-        <v>0.9777</v>
+        <v>0.9295</v>
       </c>
       <c r="J170" t="n">
-        <v>19.554</v>
+        <v>18.59</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.29</v>
       </c>
       <c r="I171" t="n">
-        <v>0.7229</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="J171" t="n">
-        <v>14.458</v>
+        <v>14.002</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.61</v>
       </c>
       <c r="I172" t="n">
-        <v>1.2865</v>
+        <v>1.258</v>
       </c>
       <c r="J172" t="n">
-        <v>38.595</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.21</v>
       </c>
       <c r="I173" t="n">
-        <v>0.587</v>
+        <v>0.5687</v>
       </c>
       <c r="J173" t="n">
-        <v>17.61</v>
+        <v>17.061</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.14</v>
       </c>
       <c r="I174" t="n">
-        <v>0.4153</v>
+        <v>0.4128</v>
       </c>
       <c r="J174" t="n">
-        <v>12.459</v>
+        <v>12.384</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.04</v>
       </c>
       <c r="I175" t="n">
-        <v>0.1242</v>
+        <v>0.1413</v>
       </c>
       <c r="J175" t="n">
-        <v>3.726</v>
+        <v>4.239</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.9</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3984</v>
+        <v>-0.3766</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.952</v>
+        <v>-11.298</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.08</v>
       </c>
       <c r="I177" t="n">
-        <v>0.2393</v>
+        <v>0.2375</v>
       </c>
       <c r="J177" t="n">
-        <v>7.179</v>
+        <v>7.125</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.07</v>
       </c>
       <c r="I178" t="n">
-        <v>0.217</v>
+        <v>0.2159</v>
       </c>
       <c r="J178" t="n">
-        <v>6.51</v>
+        <v>6.477</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.0775</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="J179" t="n">
-        <v>-2.325</v>
+        <v>-2.727</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.82</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2051</v>
+        <v>-0.2217</v>
       </c>
       <c r="J180" t="n">
-        <v>-6.153</v>
+        <v>-6.651</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.52</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4897</v>
+        <v>-0.4967</v>
       </c>
       <c r="J181" t="n">
-        <v>-14.691</v>
+        <v>-14.901</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.54</v>
       </c>
       <c r="I182" t="n">
-        <v>1.1583</v>
+        <v>1.1288</v>
       </c>
       <c r="J182" t="n">
-        <v>24.3243</v>
+        <v>23.7048</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.46</v>
       </c>
       <c r="I183" t="n">
-        <v>1.0603</v>
+        <v>1.0195</v>
       </c>
       <c r="J183" t="n">
-        <v>22.2663</v>
+        <v>21.4095</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.37</v>
       </c>
       <c r="I184" t="n">
-        <v>0.9133</v>
+        <v>0.8652</v>
       </c>
       <c r="J184" t="n">
-        <v>19.1793</v>
+        <v>18.1692</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.3</v>
       </c>
       <c r="I185" t="n">
-        <v>0.7632</v>
+        <v>0.7323</v>
       </c>
       <c r="J185" t="n">
-        <v>16.0272</v>
+        <v>15.3783</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.14</v>
       </c>
       <c r="I186" t="n">
-        <v>0.3747</v>
+        <v>0.3847</v>
       </c>
       <c r="J186" t="n">
-        <v>7.8687</v>
+        <v>8.0787</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.36</v>
       </c>
       <c r="I187" t="n">
-        <v>0.873</v>
+        <v>0.8041</v>
       </c>
       <c r="J187" t="n">
-        <v>18.333</v>
+        <v>16.8861</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2001</v>
+        <v>-0.2202</v>
       </c>
       <c r="J188" t="n">
-        <v>-4.2021</v>
+        <v>-4.6242</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.65</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.351</v>
+        <v>-0.3678</v>
       </c>
       <c r="J189" t="n">
-        <v>-7.371</v>
+        <v>-7.7238</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.62</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3791</v>
+        <v>-0.3947</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.9611</v>
+        <v>-8.2887</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.33</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.6476</v>
+        <v>-0.6463</v>
       </c>
       <c r="J191" t="n">
-        <v>-13.5996</v>
+        <v>-13.5723</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2572/event_2572_evp_summary.xlsx
+++ b/database/event/2572/event_2572_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.7108</v>
+        <v>4.6838</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7259</v>
+        <v>0.7217</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5202</v>
+        <v>1.5279</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7108</v>
+        <v>4.6838</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6814</v>
+        <v>2.7352</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0294</v>
+        <v>1.9486</v>
       </c>
       <c r="H2" t="n">
-        <v>3.9528</v>
+        <v>3.8266</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1345</v>
+        <v>2.1485</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0294</v>
+        <v>1.9486</v>
       </c>
       <c r="K2" t="n">
         <v>50</v>
@@ -529,7 +529,7 @@
         <v>57</v>
       </c>
       <c r="M2" t="n">
-        <v>4.1639</v>
+        <v>4.0971</v>
       </c>
       <c r="N2" t="n">
         <v>107</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.6411</v>
+        <v>3.7061</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5611</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0333</v>
+        <v>1.0825</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6411</v>
+        <v>3.7061</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5627</v>
+        <v>2.6207</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0784</v>
+        <v>1.0854</v>
       </c>
       <c r="H3" t="n">
-        <v>3.561</v>
+        <v>3.3964</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9229</v>
+        <v>1.907</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0784</v>
+        <v>1.0854</v>
       </c>
       <c r="K3" t="n">
         <v>57</v>
@@ -575,7 +575,7 @@
         <v>50</v>
       </c>
       <c r="M3" t="n">
-        <v>3.0013</v>
+        <v>2.9924</v>
       </c>
       <c r="N3" t="n">
         <v>107</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.4051</v>
+        <v>3.298</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.5082</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9258999999999999</v>
+        <v>0.8966</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4051</v>
+        <v>3.298</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0593</v>
+        <v>3.0247</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3458</v>
+        <v>0.2733</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1997</v>
+        <v>4.9134</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8078</v>
+        <v>2.7587</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3458</v>
+        <v>0.2733</v>
       </c>
       <c r="K4" t="n">
         <v>115</v>
@@ -621,7 +621,7 @@
         <v>56</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1536</v>
+        <v>3.032</v>
       </c>
       <c r="N4" t="n">
         <v>171</v>
@@ -630,369 +630,369 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>kNgV-</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.2862</v>
+        <v>3.2882</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5064</v>
+        <v>0.5067</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8717</v>
+        <v>0.8921</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2862</v>
+        <v>3.2882</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3664</v>
+        <v>2.3558</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.08019999999999999</v>
+        <v>0.9324</v>
       </c>
       <c r="H5" t="n">
-        <v>6.2129</v>
+        <v>2.4021</v>
       </c>
       <c r="I5" t="n">
-        <v>3.3549</v>
+        <v>1.3487</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.08019999999999999</v>
+        <v>0.9324</v>
       </c>
       <c r="K5" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="L5" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2747</v>
+        <v>2.2811</v>
       </c>
       <c r="N5" t="n">
-        <v>148</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>kNgV-</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.2356</v>
+        <v>3.1971</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4986</v>
+        <v>0.4926</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8487</v>
+        <v>0.8506</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2356</v>
+        <v>3.1971</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2632</v>
+        <v>3.2785</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9724</v>
+        <v>-0.0814</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5728</v>
+        <v>5.8664</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3893</v>
+        <v>3.2938</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9724</v>
+        <v>-0.0814</v>
       </c>
       <c r="K6" t="n">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="L6" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="M6" t="n">
-        <v>2.3617</v>
+        <v>3.2124</v>
       </c>
       <c r="N6" t="n">
-        <v>107</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.0904</v>
+        <v>2.9536</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4762</v>
+        <v>0.4551</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7826</v>
+        <v>0.7397</v>
       </c>
       <c r="E7" t="n">
-        <v>3.0904</v>
+        <v>2.9536</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7411</v>
+        <v>3.2884</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3493</v>
+        <v>-0.3348</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7411</v>
+        <v>5.9033</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9402</v>
+        <v>3.3145</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3493</v>
+        <v>-0.3348</v>
       </c>
       <c r="K7" t="n">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="L7" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M7" t="n">
-        <v>2.2895</v>
+        <v>2.9797</v>
       </c>
       <c r="N7" t="n">
-        <v>107</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.0035</v>
+        <v>2.9071</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4628</v>
+        <v>0.448</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7431</v>
+        <v>0.7185</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0035</v>
+        <v>2.9071</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0808</v>
+        <v>3.2923</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9227</v>
+        <v>-0.3852</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0808</v>
+        <v>5.9182</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5836</v>
+        <v>3.3229</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9227</v>
+        <v>-0.3852</v>
       </c>
       <c r="K8" t="n">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="L8" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M8" t="n">
-        <v>2.5063</v>
+        <v>2.9377</v>
       </c>
       <c r="N8" t="n">
-        <v>107</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9918</v>
+        <v>2.8606</v>
       </c>
       <c r="C9" t="n">
-        <v>0.461</v>
+        <v>0.4408</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7377</v>
+        <v>0.6974</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9918</v>
+        <v>2.8606</v>
       </c>
       <c r="F9" t="n">
-        <v>3.3628</v>
+        <v>1.5459</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.371</v>
+        <v>1.3147</v>
       </c>
       <c r="H9" t="n">
-        <v>6.2008</v>
+        <v>1.5459</v>
       </c>
       <c r="I9" t="n">
-        <v>3.3484</v>
+        <v>0.868</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.371</v>
+        <v>1.3147</v>
       </c>
       <c r="K9" t="n">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="L9" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9774</v>
+        <v>2.1827</v>
       </c>
       <c r="N9" t="n">
-        <v>171</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9815</v>
+        <v>2.852</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4594</v>
+        <v>0.4395</v>
       </c>
       <c r="D10" t="n">
-        <v>0.733</v>
+        <v>0.6934</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9815</v>
+        <v>2.852</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4963</v>
+        <v>3.0666</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4852</v>
+        <v>-0.2146</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4963</v>
+        <v>5.0708</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8080000000000001</v>
+        <v>2.8471</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4852</v>
+        <v>-0.2146</v>
       </c>
       <c r="K10" t="n">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="L10" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M10" t="n">
-        <v>2.2932</v>
+        <v>2.6325</v>
       </c>
       <c r="N10" t="n">
-        <v>107</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9743</v>
+        <v>2.7992</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4583</v>
+        <v>0.4313</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7298</v>
+        <v>0.6694</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9743</v>
+        <v>2.7992</v>
       </c>
       <c r="F11" t="n">
-        <v>3.1311</v>
+        <v>2.7583</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1568</v>
+        <v>0.0409</v>
       </c>
       <c r="H11" t="n">
-        <v>5.4364</v>
+        <v>3.9133</v>
       </c>
       <c r="I11" t="n">
-        <v>2.9356</v>
+        <v>2.1972</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1568</v>
+        <v>0.0409</v>
       </c>
       <c r="K11" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="L11" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7788</v>
+        <v>2.2381</v>
       </c>
       <c r="N11" t="n">
-        <v>148</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.937</v>
+        <v>2.7807</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4526</v>
+        <v>0.4285</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7128</v>
+        <v>0.661</v>
       </c>
       <c r="E12" t="n">
-        <v>2.937</v>
+        <v>2.7807</v>
       </c>
       <c r="F12" t="n">
-        <v>3.3574</v>
+        <v>0.9283</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4204</v>
+        <v>1.8524</v>
       </c>
       <c r="H12" t="n">
-        <v>6.1832</v>
+        <v>0.9283</v>
       </c>
       <c r="I12" t="n">
-        <v>3.3389</v>
+        <v>0.5212</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4204</v>
+        <v>1.8524</v>
       </c>
       <c r="K12" t="n">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="L12" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9185</v>
+        <v>2.3736</v>
       </c>
       <c r="N12" t="n">
-        <v>171</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7313</v>
+        <v>2.7597</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4209</v>
+        <v>0.4252</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6191</v>
+        <v>0.6514</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7313</v>
+        <v>2.7597</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7992</v>
+        <v>2.8457</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0679</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>4.3414</v>
+        <v>4.2412</v>
       </c>
       <c r="I13" t="n">
-        <v>2.3443</v>
+        <v>2.3813</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.0679</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="K13" t="n">
         <v>115</v>
@@ -1035,7 +1035,7 @@
         <v>56</v>
       </c>
       <c r="M13" t="n">
-        <v>2.2764</v>
+        <v>2.2953</v>
       </c>
       <c r="N13" t="n">
         <v>171</v>
@@ -1044,35 +1044,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.7298</v>
+        <v>2.7333</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4206</v>
+        <v>0.4212</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6185</v>
+        <v>0.6394</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7298</v>
+        <v>2.7333</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7098</v>
+        <v>2.3688</v>
       </c>
       <c r="G14" t="n">
-        <v>0.02</v>
+        <v>0.3645</v>
       </c>
       <c r="H14" t="n">
-        <v>4.0464</v>
+        <v>2.4509</v>
       </c>
       <c r="I14" t="n">
-        <v>2.185</v>
+        <v>1.3761</v>
       </c>
       <c r="J14" t="n">
-        <v>0.02</v>
+        <v>0.3645</v>
       </c>
       <c r="K14" t="n">
         <v>50</v>
@@ -1081,7 +1081,7 @@
         <v>57</v>
       </c>
       <c r="M14" t="n">
-        <v>2.205</v>
+        <v>1.7406</v>
       </c>
       <c r="N14" t="n">
         <v>107</v>
@@ -1090,44 +1090,44 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5944</v>
+        <v>2.7307</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3998</v>
+        <v>0.4208</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5568</v>
+        <v>0.6382</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5944</v>
+        <v>2.7307</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2635</v>
+        <v>1.3089</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3309</v>
+        <v>1.4218</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5739</v>
+        <v>1.3089</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3899</v>
+        <v>0.7349</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3309</v>
+        <v>1.4218</v>
       </c>
       <c r="K15" t="n">
+        <v>57</v>
+      </c>
+      <c r="L15" t="n">
         <v>50</v>
       </c>
-      <c r="L15" t="n">
-        <v>57</v>
-      </c>
       <c r="M15" t="n">
-        <v>1.7208</v>
+        <v>2.1567</v>
       </c>
       <c r="N15" t="n">
         <v>107</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.4413</v>
+        <v>2.5673</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3762</v>
+        <v>0.3956</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4871</v>
+        <v>0.5637</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4413</v>
+        <v>2.5673</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5311</v>
+        <v>2.6376</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0898</v>
+        <v>-0.0703</v>
       </c>
       <c r="H16" t="n">
-        <v>3.4567</v>
+        <v>3.46</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8666</v>
+        <v>1.9427</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0898</v>
+        <v>-0.0703</v>
       </c>
       <c r="K16" t="n">
         <v>99</v>
@@ -1173,7 +1173,7 @@
         <v>49</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7768</v>
+        <v>1.8724</v>
       </c>
       <c r="N16" t="n">
         <v>148</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.3534</v>
+        <v>2.4259</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3626</v>
+        <v>0.3738</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4471</v>
+        <v>0.4993</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3534</v>
+        <v>2.4259</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7024</v>
+        <v>2.7412</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.349</v>
+        <v>-0.3153</v>
       </c>
       <c r="H17" t="n">
-        <v>4.0221</v>
+        <v>3.8492</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1719</v>
+        <v>2.1612</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.349</v>
+        <v>-0.3153</v>
       </c>
       <c r="K17" t="n">
         <v>99</v>
@@ -1219,7 +1219,7 @@
         <v>49</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8229</v>
+        <v>1.8459</v>
       </c>
       <c r="N17" t="n">
         <v>148</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.3127</v>
+        <v>2.1947</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3564</v>
+        <v>0.3382</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4286</v>
+        <v>0.394</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3127</v>
+        <v>2.1947</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3127</v>
+        <v>2.1947</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.3369</v>
+        <v>2.1947</v>
       </c>
       <c r="I18" t="n">
-        <v>2.3369</v>
+        <v>2.1947</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.3369</v>
+        <v>2.1947</v>
       </c>
       <c r="N18" t="n">
         <v>100</v>
@@ -1274,93 +1274,93 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SHOOWTiME</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.4682</v>
+        <v>1.6642</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2262</v>
+        <v>0.2564</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0442</v>
+        <v>0.1523</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4682</v>
+        <v>1.6642</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4682</v>
+        <v>-0.8218</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2.486</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4682</v>
+        <v>-0.8218</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4682</v>
+        <v>-0.4614</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>2.486</v>
       </c>
       <c r="K19" t="n">
-        <v>125</v>
+        <v>57</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4682</v>
+        <v>2.0246</v>
       </c>
       <c r="N19" t="n">
-        <v>125</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>SHOOWTiME</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4191</v>
+        <v>1.4008</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2187</v>
+        <v>0.2158</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0218</v>
+        <v>0.0323</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4191</v>
+        <v>1.4008</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9896</v>
+        <v>1.4008</v>
       </c>
       <c r="G20" t="n">
-        <v>2.4087</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9896</v>
+        <v>1.4008</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5344</v>
+        <v>1.4008</v>
       </c>
       <c r="J20" t="n">
-        <v>2.4087</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>57</v>
+        <v>125</v>
       </c>
       <c r="L20" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.8743</v>
+        <v>1.4008</v>
       </c>
       <c r="N20" t="n">
-        <v>107</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.334</v>
+        <v>1.3208</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2056</v>
+        <v>0.2035</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0169</v>
+        <v>-0.0041</v>
       </c>
       <c r="E21" t="n">
-        <v>1.334</v>
+        <v>1.3208</v>
       </c>
       <c r="F21" t="n">
-        <v>1.334</v>
+        <v>1.3208</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.334</v>
+        <v>1.3208</v>
       </c>
       <c r="I21" t="n">
-        <v>1.334</v>
+        <v>1.3208</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.334</v>
+        <v>1.3208</v>
       </c>
       <c r="N21" t="n">
         <v>125</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0313</v>
+        <v>1.0064</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1589</v>
+        <v>0.1551</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1547</v>
+        <v>-0.1473</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0313</v>
+        <v>1.0064</v>
       </c>
       <c r="F22" t="n">
-        <v>1.8297</v>
+        <v>1.7823</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7984</v>
+        <v>-0.7759</v>
       </c>
       <c r="H22" t="n">
-        <v>1.8297</v>
+        <v>1.7823</v>
       </c>
       <c r="I22" t="n">
-        <v>0.988</v>
+        <v>1.0007</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7984</v>
+        <v>-0.7759</v>
       </c>
       <c r="K22" t="n">
         <v>99</v>
@@ -1449,7 +1449,7 @@
         <v>49</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1896</v>
+        <v>0.2247999999999999</v>
       </c>
       <c r="N22" t="n">
         <v>148</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9291</v>
+        <v>0.8776</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1432</v>
+        <v>0.1352</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2013</v>
+        <v>-0.206</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9291</v>
+        <v>0.8776</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9291</v>
+        <v>0.8776</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9291</v>
+        <v>0.8776</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9291</v>
+        <v>0.8776</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9291</v>
+        <v>0.8776</v>
       </c>
       <c r="N23" t="n">
         <v>76</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8815</v>
+        <v>0.845</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1358</v>
+        <v>0.1302</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2229</v>
+        <v>-0.2209</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8815</v>
+        <v>0.845</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8815</v>
+        <v>0.845</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8815</v>
+        <v>0.845</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8815</v>
+        <v>0.845</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8815</v>
+        <v>0.845</v>
       </c>
       <c r="N24" t="n">
         <v>100</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7887999999999999</v>
+        <v>0.745</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1215</v>
+        <v>0.1148</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2651</v>
+        <v>-0.2664</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7887999999999999</v>
+        <v>0.745</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7887999999999999</v>
+        <v>0.745</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7887999999999999</v>
+        <v>0.745</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7887999999999999</v>
+        <v>0.745</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7887999999999999</v>
+        <v>0.745</v>
       </c>
       <c r="N25" t="n">
         <v>100</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6624</v>
+        <v>0.7249</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1021</v>
+        <v>0.1117</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3227</v>
+        <v>-0.2756</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6624</v>
+        <v>0.7249</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6624</v>
+        <v>0.7249</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6624</v>
+        <v>0.7249</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6624</v>
+        <v>0.7249</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6624</v>
+        <v>0.7249</v>
       </c>
       <c r="N26" t="n">
         <v>100</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5233</v>
+        <v>0.5255</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0806</v>
+        <v>0.081</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.386</v>
+        <v>-0.3664</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5233</v>
+        <v>0.5255</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5233</v>
+        <v>0.5255</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5233</v>
+        <v>0.5255</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5233</v>
+        <v>0.5255</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.5233</v>
+        <v>0.5255</v>
       </c>
       <c r="N27" t="n">
         <v>100</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3424</v>
+        <v>0.2736</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0528</v>
+        <v>0.0422</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4683</v>
+        <v>-0.4812</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3424</v>
+        <v>0.2736</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3424</v>
+        <v>0.2736</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3424</v>
+        <v>0.2736</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3424</v>
+        <v>0.2736</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3424</v>
+        <v>0.2736</v>
       </c>
       <c r="N28" t="n">
         <v>76</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.033</v>
+        <v>0.0326</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0051</v>
+        <v>0.005</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6092</v>
+        <v>-0.5909</v>
       </c>
       <c r="E29" t="n">
-        <v>0.033</v>
+        <v>0.0326</v>
       </c>
       <c r="F29" t="n">
-        <v>0.033</v>
+        <v>0.0326</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.033</v>
+        <v>0.0326</v>
       </c>
       <c r="I29" t="n">
-        <v>0.033</v>
+        <v>0.0326</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.033</v>
+        <v>0.0326</v>
       </c>
       <c r="N29" t="n">
         <v>125</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1058</v>
+        <v>-0.0893</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0163</v>
+        <v>-0.0138</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6724</v>
+        <v>-0.6465</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1058</v>
+        <v>-0.0893</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1058</v>
+        <v>-0.0893</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1058</v>
+        <v>-0.0893</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1058</v>
+        <v>-0.0893</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1058</v>
+        <v>-0.0893</v>
       </c>
       <c r="N30" t="n">
         <v>125</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3246</v>
+        <v>-0.3566</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.05</v>
+        <v>-0.0549</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.772</v>
+        <v>-0.7682</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3246</v>
+        <v>-0.3566</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3246</v>
+        <v>-0.3566</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3246</v>
+        <v>-0.3566</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3246</v>
+        <v>-0.3566</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3246</v>
+        <v>-0.3566</v>
       </c>
       <c r="N31" t="n">
         <v>76</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4238</v>
+        <v>-0.4643</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0653</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8171</v>
+        <v>-0.8173</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4238</v>
+        <v>-0.4643</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4238</v>
+        <v>-0.4643</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4238</v>
+        <v>-0.4643</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4238</v>
+        <v>-0.4643</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4238</v>
+        <v>-0.4643</v>
       </c>
       <c r="N32" t="n">
         <v>72</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4242</v>
+        <v>-0.475</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0654</v>
+        <v>-0.0732</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8173</v>
+        <v>-0.8222</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4242</v>
+        <v>-0.475</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4242</v>
+        <v>-0.475</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4242</v>
+        <v>-0.475</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4242</v>
+        <v>-0.475</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4242</v>
+        <v>-0.475</v>
       </c>
       <c r="N33" t="n">
         <v>72</v>
@@ -1964,185 +1964,185 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MarKE</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.543</v>
+        <v>-0.541</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0837</v>
+        <v>-0.0834</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8714</v>
+        <v>-0.8522</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.543</v>
+        <v>-0.541</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.543</v>
+        <v>-0.541</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.543</v>
+        <v>-0.541</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.543</v>
+        <v>-0.541</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.543</v>
+        <v>-0.541</v>
       </c>
       <c r="N34" t="n">
-        <v>72</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>MarKE</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.5941</v>
+        <v>-0.5625</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0915</v>
+        <v>-0.0867</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8946</v>
+        <v>-0.862</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5941</v>
+        <v>-0.5625</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.5941</v>
+        <v>-0.5625</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.5941</v>
+        <v>-0.5625</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5941</v>
+        <v>-0.5625</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5941</v>
+        <v>-0.5625</v>
       </c>
       <c r="N35" t="n">
-        <v>125</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>guishorro</t>
+          <t>ptr</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6158</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0949</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9045</v>
+        <v>-0.8958</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6158</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.6158</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.6158</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6158</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.6158</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ptr</t>
+          <t>guishorro</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.6853</v>
+        <v>-0.6523</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1056</v>
+        <v>-0.1005</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9362</v>
+        <v>-0.9029</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.6853</v>
+        <v>-0.6523</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.6853</v>
+        <v>-0.6523</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.6853</v>
+        <v>-0.6523</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.6853</v>
+        <v>-0.6523</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.6853</v>
+        <v>-0.6523</v>
       </c>
       <c r="N37" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38">
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.7652</v>
+        <v>-0.7128</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1179</v>
+        <v>-0.1098</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9725</v>
+        <v>-0.9305</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.7652</v>
+        <v>-0.7128</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.5802</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.185</v>
+        <v>-0.1377</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.5802</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3133</v>
+        <v>-0.3229</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.185</v>
+        <v>-0.1377</v>
       </c>
       <c r="K38" t="n">
         <v>50</v>
@@ -2185,7 +2185,7 @@
         <v>57</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.4983</v>
+        <v>-0.4606</v>
       </c>
       <c r="N38" t="n">
         <v>107</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3924</v>
+        <v>-1.3394</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2146</v>
+        <v>-0.2064</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2581</v>
+        <v>-1.2159</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3924</v>
+        <v>-1.3394</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.9274</v>
+        <v>-0.8556</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.465</v>
+        <v>-0.4838</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9274</v>
+        <v>-0.8556</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.5008</v>
+        <v>-0.4804</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.465</v>
+        <v>-0.4838</v>
       </c>
       <c r="K39" t="n">
         <v>115</v>
@@ -2231,7 +2231,7 @@
         <v>56</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.9658</v>
+        <v>-0.9641999999999999</v>
       </c>
       <c r="N39" t="n">
         <v>171</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.467</v>
+        <v>-1.4848</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.226</v>
+        <v>-0.2288</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.292</v>
+        <v>-1.2822</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.467</v>
+        <v>-1.4848</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.467</v>
+        <v>-1.4848</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.467</v>
+        <v>-1.4848</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.467</v>
+        <v>-1.4848</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.467</v>
+        <v>-1.4848</v>
       </c>
       <c r="N40" t="n">
         <v>76</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.4967</v>
+        <v>-1.4964</v>
       </c>
       <c r="C41" t="n">
         <v>-0.2306</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3055</v>
+        <v>-1.2875</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.4967</v>
+        <v>-1.4964</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.4967</v>
+        <v>-1.4964</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.4967</v>
+        <v>-1.4964</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.4967</v>
+        <v>-1.4964</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.4967</v>
+        <v>-1.4964</v>
       </c>
       <c r="N41" t="n">
         <v>72</v>
@@ -2429,10 +2429,10 @@
         <v>1.3</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6274</v>
+        <v>0.5733</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6274</v>
+        <v>0.5733</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.95</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08</v>
+        <v>-0.0668</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.08</v>
+        <v>-0.0668</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.85</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1932</v>
+        <v>-0.1735</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1932</v>
+        <v>-0.1735</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.78</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2633</v>
+        <v>-0.2439</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2633</v>
+        <v>-0.2439</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.66</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3756</v>
+        <v>-0.3623</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3756</v>
+        <v>-0.3623</v>
       </c>
     </row>
     <row r="7">
@@ -2669,10 +2669,10 @@
         <v>1.36</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8582</v>
+        <v>0.8406</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8582</v>
+        <v>0.8406</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.33</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8002</v>
+        <v>0.779</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8002</v>
+        <v>0.779</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.18</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4921</v>
+        <v>0.4604</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4921</v>
+        <v>0.4604</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.02</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0553</v>
+        <v>0.0389</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0553</v>
+        <v>0.0389</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>2.1</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6661</v>
+        <v>1.7029</v>
       </c>
       <c r="J12" t="n">
-        <v>36.6542</v>
+        <v>37.4638</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.41</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8069</v>
+        <v>0.7962</v>
       </c>
       <c r="J13" t="n">
-        <v>17.7518</v>
+        <v>17.5164</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.22</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.5291</v>
       </c>
       <c r="J14" t="n">
-        <v>11.6996</v>
+        <v>11.6402</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.11</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3076</v>
+        <v>0.2755</v>
       </c>
       <c r="J15" t="n">
-        <v>6.7672</v>
+        <v>6.061</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.05</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1404</v>
+        <v>0.1132</v>
       </c>
       <c r="J16" t="n">
-        <v>3.0888</v>
+        <v>2.4904</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0677</v>
+        <v>-0.0539</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.4894</v>
+        <v>-1.1858</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.89</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1305</v>
+        <v>-0.1151</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.871</v>
+        <v>-2.5322</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2178</v>
+        <v>-0.2023</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.7916</v>
+        <v>-4.4506</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.58</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4281</v>
+        <v>-0.419</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.418200000000001</v>
+        <v>-9.218</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.46</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5332</v>
+        <v>-0.5361</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.7304</v>
+        <v>-11.7942</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.62</v>
       </c>
       <c r="I22" t="n">
-        <v>1.123</v>
+        <v>1.1165</v>
       </c>
       <c r="J22" t="n">
-        <v>30.321</v>
+        <v>30.1455</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.36</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7622</v>
+        <v>0.7467</v>
       </c>
       <c r="J23" t="n">
-        <v>20.5794</v>
+        <v>20.1609</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.18</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4866</v>
+        <v>0.468</v>
       </c>
       <c r="J24" t="n">
-        <v>13.1382</v>
+        <v>12.636</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.92</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3227</v>
+        <v>-0.2822</v>
       </c>
       <c r="J25" t="n">
-        <v>-8.712899999999999</v>
+        <v>-7.6194</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.84</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.4898</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.2749</v>
+        <v>-13.2246</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.16</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3764</v>
+        <v>0.3215</v>
       </c>
       <c r="J27" t="n">
-        <v>10.1628</v>
+        <v>8.6805</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.01</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0503</v>
+        <v>0.0337</v>
       </c>
       <c r="J28" t="n">
-        <v>1.3581</v>
+        <v>0.9099</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.99</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0221</v>
+        <v>-0.0164</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.5967</v>
+        <v>-0.4428</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1312</v>
+        <v>-0.113</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.5424</v>
+        <v>-3.051</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.67</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3703</v>
+        <v>-0.3569</v>
       </c>
       <c r="J31" t="n">
-        <v>-9.998100000000001</v>
+        <v>-9.6363</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.32</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7247</v>
+        <v>0.7089</v>
       </c>
       <c r="J32" t="n">
-        <v>21.741</v>
+        <v>21.267</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.16</v>
       </c>
       <c r="I33" t="n">
-        <v>0.465</v>
+        <v>0.4337</v>
       </c>
       <c r="J33" t="n">
-        <v>13.95</v>
+        <v>13.011</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.12</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3779</v>
+        <v>0.3378</v>
       </c>
       <c r="J34" t="n">
-        <v>11.337</v>
+        <v>10.134</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.98</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.112</v>
+        <v>-0.0858</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.36</v>
+        <v>-2.574</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.79</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6254999999999999</v>
+        <v>-0.5888</v>
       </c>
       <c r="J36" t="n">
-        <v>-18.765</v>
+        <v>-17.664</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.05</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1587</v>
+        <v>0.1223</v>
       </c>
       <c r="J37" t="n">
-        <v>4.761</v>
+        <v>3.669</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.04</v>
       </c>
       <c r="I38" t="n">
-        <v>0.135</v>
+        <v>0.102</v>
       </c>
       <c r="J38" t="n">
-        <v>4.05</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.01</v>
       </c>
       <c r="I39" t="n">
-        <v>0.052</v>
+        <v>0.035</v>
       </c>
       <c r="J39" t="n">
-        <v>1.56</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.82</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2266</v>
+        <v>-0.2064</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.798</v>
+        <v>-6.192</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.77</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.276</v>
+        <v>-0.2568</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.279999999999999</v>
+        <v>-7.704</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.52</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9701</v>
+        <v>0.9569</v>
       </c>
       <c r="J42" t="n">
-        <v>25.2226</v>
+        <v>24.8794</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.33</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7062</v>
+        <v>0.6942</v>
       </c>
       <c r="J43" t="n">
-        <v>18.3612</v>
+        <v>18.0492</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.31</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6773</v>
+        <v>0.6664</v>
       </c>
       <c r="J44" t="n">
-        <v>17.6098</v>
+        <v>17.3264</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.28</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6337</v>
+        <v>0.6246</v>
       </c>
       <c r="J45" t="n">
-        <v>16.4762</v>
+        <v>16.2396</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.91</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.365</v>
+        <v>-0.326</v>
       </c>
       <c r="J46" t="n">
-        <v>-9.49</v>
+        <v>-8.476000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.06</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2108</v>
+        <v>0.1713</v>
       </c>
       <c r="J47" t="n">
-        <v>5.4808</v>
+        <v>4.4538</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.89</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1444</v>
+        <v>-0.1284</v>
       </c>
       <c r="J48" t="n">
-        <v>-3.7544</v>
+        <v>-3.3384</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.89</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1444</v>
+        <v>-0.1284</v>
       </c>
       <c r="J49" t="n">
-        <v>-3.7544</v>
+        <v>-3.3384</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2266</v>
+        <v>-0.2083</v>
       </c>
       <c r="J50" t="n">
-        <v>-5.8916</v>
+        <v>-5.4158</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.49</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.517</v>
+        <v>-0.5188</v>
       </c>
       <c r="J51" t="n">
-        <v>-13.442</v>
+        <v>-13.4888</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.71</v>
       </c>
       <c r="I52" t="n">
-        <v>1.3901</v>
+        <v>1.4175</v>
       </c>
       <c r="J52" t="n">
-        <v>38.9228</v>
+        <v>39.69</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.14</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4128</v>
+        <v>0.3775</v>
       </c>
       <c r="J53" t="n">
-        <v>11.5584</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.13</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3888</v>
+        <v>0.3537</v>
       </c>
       <c r="J54" t="n">
-        <v>10.8864</v>
+        <v>9.903600000000001</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.98</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1313</v>
+        <v>-0.104</v>
       </c>
       <c r="J55" t="n">
-        <v>-3.6764</v>
+        <v>-2.912</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2642</v>
+        <v>-0.2257</v>
       </c>
       <c r="J56" t="n">
-        <v>-7.3976</v>
+        <v>-6.3196</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.24</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5365</v>
+        <v>0.4819</v>
       </c>
       <c r="J57" t="n">
-        <v>15.022</v>
+        <v>13.4932</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.16</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3951</v>
+        <v>0.3414</v>
       </c>
       <c r="J58" t="n">
-        <v>11.0628</v>
+        <v>9.559200000000001</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.88</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1599</v>
+        <v>-0.1419</v>
       </c>
       <c r="J59" t="n">
-        <v>-4.4772</v>
+        <v>-3.9732</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.6</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4268</v>
+        <v>-0.4182</v>
       </c>
       <c r="J60" t="n">
-        <v>-11.9504</v>
+        <v>-11.7096</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.54</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4793</v>
+        <v>-0.4767</v>
       </c>
       <c r="J61" t="n">
-        <v>-13.4204</v>
+        <v>-13.3476</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.59</v>
       </c>
       <c r="I62" t="n">
-        <v>1.1799</v>
+        <v>1.1973</v>
       </c>
       <c r="J62" t="n">
-        <v>24.7779</v>
+        <v>25.1433</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.54</v>
       </c>
       <c r="I63" t="n">
-        <v>1.1165</v>
+        <v>1.1331</v>
       </c>
       <c r="J63" t="n">
-        <v>23.4465</v>
+        <v>23.7951</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.43</v>
       </c>
       <c r="I64" t="n">
-        <v>0.9628</v>
+        <v>0.9641</v>
       </c>
       <c r="J64" t="n">
-        <v>20.2188</v>
+        <v>20.2461</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.4</v>
       </c>
       <c r="I65" t="n">
-        <v>0.9105</v>
+        <v>0.9061</v>
       </c>
       <c r="J65" t="n">
-        <v>19.1205</v>
+        <v>19.0281</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.35</v>
       </c>
       <c r="I66" t="n">
-        <v>0.8168</v>
+        <v>0.8054</v>
       </c>
       <c r="J66" t="n">
-        <v>17.1528</v>
+        <v>16.9134</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.0295</v>
+        <v>-0.0053</v>
       </c>
       <c r="J67" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.1113</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.82</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1789</v>
+        <v>-0.1607</v>
       </c>
       <c r="J68" t="n">
-        <v>-3.7569</v>
+        <v>-3.3747</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.66</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3418</v>
+        <v>-0.3323</v>
       </c>
       <c r="J69" t="n">
-        <v>-7.1778</v>
+        <v>-6.9783</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.48</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4983</v>
+        <v>-0.4963</v>
       </c>
       <c r="J70" t="n">
-        <v>-10.4643</v>
+        <v>-10.4223</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.12</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.8149</v>
+        <v>-0.8732</v>
       </c>
       <c r="J71" t="n">
-        <v>-17.1129</v>
+        <v>-18.3372</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.26</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5666</v>
+        <v>0.5118</v>
       </c>
       <c r="J72" t="n">
-        <v>15.2982</v>
+        <v>13.8186</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.9</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.1391</v>
+        <v>-0.1218</v>
       </c>
       <c r="J73" t="n">
-        <v>-3.7557</v>
+        <v>-3.2886</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.82</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2225</v>
+        <v>-0.2028</v>
       </c>
       <c r="J74" t="n">
-        <v>-6.0075</v>
+        <v>-5.4756</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2325</v>
+        <v>-0.2128</v>
       </c>
       <c r="J75" t="n">
-        <v>-6.2775</v>
+        <v>-5.7456</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.68</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.356</v>
+        <v>-0.3412</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.612</v>
+        <v>-9.212400000000001</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.3</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7699</v>
+        <v>0.7415</v>
       </c>
       <c r="J77" t="n">
-        <v>20.7873</v>
+        <v>20.0205</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.21</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5782</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="J78" t="n">
-        <v>15.6114</v>
+        <v>14.6016</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.15</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4423</v>
+        <v>0.4038</v>
       </c>
       <c r="J79" t="n">
-        <v>11.9421</v>
+        <v>10.9026</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.12</v>
       </c>
       <c r="I80" t="n">
-        <v>0.3715</v>
+        <v>0.3341</v>
       </c>
       <c r="J80" t="n">
-        <v>10.0305</v>
+        <v>9.0207</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.84</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5178</v>
+        <v>-0.4773</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.9806</v>
+        <v>-12.8871</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.3</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6014</v>
+        <v>0.543</v>
       </c>
       <c r="J82" t="n">
-        <v>15.6364</v>
+        <v>14.118</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.05</v>
       </c>
       <c r="I83" t="n">
-        <v>0.15</v>
+        <v>0.1153</v>
       </c>
       <c r="J83" t="n">
-        <v>3.9</v>
+        <v>2.9978</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.99</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.0247</v>
+        <v>-0.0179</v>
       </c>
       <c r="J84" t="n">
-        <v>-0.6422</v>
+        <v>-0.4654</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.8</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2511</v>
+        <v>-0.2312</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.5286</v>
+        <v>-6.0112</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.79</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.261</v>
+        <v>-0.2414</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.786</v>
+        <v>-6.2764</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.43</v>
       </c>
       <c r="I87" t="n">
-        <v>1.007</v>
+        <v>1.005</v>
       </c>
       <c r="J87" t="n">
-        <v>26.182</v>
+        <v>26.13</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.31</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7785</v>
+        <v>0.7519</v>
       </c>
       <c r="J88" t="n">
-        <v>20.241</v>
+        <v>19.5494</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.28</v>
       </c>
       <c r="I89" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.6871</v>
       </c>
       <c r="J89" t="n">
-        <v>18.6472</v>
+        <v>17.8646</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.08</v>
       </c>
       <c r="I90" t="n">
-        <v>0.261</v>
+        <v>0.2294</v>
       </c>
       <c r="J90" t="n">
-        <v>6.786</v>
+        <v>5.9644</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.77</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6889</v>
+        <v>-0.6585</v>
       </c>
       <c r="J91" t="n">
-        <v>-17.9114</v>
+        <v>-17.121</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.2</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4366</v>
+        <v>0.379</v>
       </c>
       <c r="J92" t="n">
-        <v>12.6614</v>
+        <v>10.991</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.04</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1263</v>
+        <v>0.0953</v>
       </c>
       <c r="J93" t="n">
-        <v>3.6627</v>
+        <v>2.7637</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.93</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1105</v>
+        <v>-0.093</v>
       </c>
       <c r="J94" t="n">
-        <v>-3.2045</v>
+        <v>-2.697</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.93</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1105</v>
+        <v>-0.093</v>
       </c>
       <c r="J95" t="n">
-        <v>-3.2045</v>
+        <v>-2.697</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.84</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2108</v>
+        <v>-0.1902</v>
       </c>
       <c r="J96" t="n">
-        <v>-6.1132</v>
+        <v>-5.5158</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.44</v>
       </c>
       <c r="I97" t="n">
-        <v>1.024</v>
+        <v>1.0251</v>
       </c>
       <c r="J97" t="n">
-        <v>29.696</v>
+        <v>29.7279</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.37</v>
       </c>
       <c r="I98" t="n">
-        <v>0.8993</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="J98" t="n">
-        <v>26.0797</v>
+        <v>25.5664</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.03</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1094</v>
+        <v>0.0886</v>
       </c>
       <c r="J99" t="n">
-        <v>3.1726</v>
+        <v>2.5694</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.01</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0315</v>
+        <v>0.0216</v>
       </c>
       <c r="J100" t="n">
-        <v>0.9135</v>
+        <v>0.6264</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.0283</v>
+        <v>-0.0227</v>
       </c>
       <c r="J101" t="n">
-        <v>-0.8207</v>
+        <v>-0.6583</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.17</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4363</v>
+        <v>0.3859</v>
       </c>
       <c r="J102" t="n">
-        <v>11.3438</v>
+        <v>10.0334</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.07</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2355</v>
+        <v>0.194</v>
       </c>
       <c r="J103" t="n">
-        <v>6.123</v>
+        <v>5.044</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.83</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.207</v>
+        <v>-0.1893</v>
       </c>
       <c r="J104" t="n">
-        <v>-5.382</v>
+        <v>-4.9218</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.66</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3665</v>
+        <v>-0.3525</v>
       </c>
       <c r="J105" t="n">
-        <v>-9.529</v>
+        <v>-9.164999999999999</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.38</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6099</v>
+        <v>-0.6263</v>
       </c>
       <c r="J106" t="n">
-        <v>-15.8574</v>
+        <v>-16.2838</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.68</v>
       </c>
       <c r="I107" t="n">
-        <v>1.3132</v>
+        <v>1.3331</v>
       </c>
       <c r="J107" t="n">
-        <v>34.1432</v>
+        <v>34.6606</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.45</v>
       </c>
       <c r="I108" t="n">
-        <v>1.0076</v>
+        <v>1.0095</v>
       </c>
       <c r="J108" t="n">
-        <v>26.1976</v>
+        <v>26.247</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.36</v>
       </c>
       <c r="I109" t="n">
-        <v>0.8489</v>
+        <v>0.8341</v>
       </c>
       <c r="J109" t="n">
-        <v>22.0714</v>
+        <v>21.6866</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.25</v>
       </c>
       <c r="I110" t="n">
-        <v>0.6341</v>
+        <v>0.6085</v>
       </c>
       <c r="J110" t="n">
-        <v>16.4866</v>
+        <v>15.821</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.95</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2601</v>
+        <v>-0.2264</v>
       </c>
       <c r="J111" t="n">
-        <v>-6.7626</v>
+        <v>-5.8864</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.11</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3096</v>
+        <v>0.2611</v>
       </c>
       <c r="J112" t="n">
-        <v>7.74</v>
+        <v>6.5275</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.04</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1557</v>
+        <v>0.1215</v>
       </c>
       <c r="J113" t="n">
-        <v>3.8925</v>
+        <v>3.0375</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.0871</v>
+        <v>-0.074</v>
       </c>
       <c r="J114" t="n">
-        <v>-2.1775</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.63</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3968</v>
+        <v>-0.3851</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.92</v>
+        <v>-9.6275</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.54</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4762</v>
+        <v>-0.4729</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.905</v>
+        <v>-11.8225</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.41</v>
       </c>
       <c r="I117" t="n">
-        <v>0.9623</v>
+        <v>0.9534</v>
       </c>
       <c r="J117" t="n">
-        <v>24.0575</v>
+        <v>23.835</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.39</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9258</v>
+        <v>0.9119</v>
       </c>
       <c r="J118" t="n">
-        <v>23.145</v>
+        <v>22.7975</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.21</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5648</v>
+        <v>0.532</v>
       </c>
       <c r="J119" t="n">
-        <v>14.12</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.17</v>
       </c>
       <c r="I120" t="n">
-        <v>0.4769</v>
+        <v>0.4432</v>
       </c>
       <c r="J120" t="n">
-        <v>11.9225</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.92</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.329</v>
+        <v>-0.2892</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.225</v>
+        <v>-7.23</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>0.47</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.4565</v>
+        <v>-0.4588</v>
       </c>
       <c r="J122" t="n">
-        <v>-7.7605</v>
+        <v>-7.7996</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.45</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.477</v>
+        <v>-0.4818</v>
       </c>
       <c r="J123" t="n">
-        <v>-8.109</v>
+        <v>-8.1906</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.37</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.5526</v>
+        <v>-0.5625</v>
       </c>
       <c r="J124" t="n">
-        <v>-9.3942</v>
+        <v>-9.5625</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.27</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.6429</v>
+        <v>-0.659</v>
       </c>
       <c r="J125" t="n">
-        <v>-10.9293</v>
+        <v>-11.203</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.25</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6624</v>
+        <v>-0.6814</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.2608</v>
+        <v>-11.5838</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>2.46</v>
       </c>
       <c r="I127" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J127" t="n">
-        <v>32.9324</v>
+        <v>33.6906</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.87</v>
       </c>
       <c r="I128" t="n">
-        <v>1.4774</v>
+        <v>1.5153</v>
       </c>
       <c r="J128" t="n">
-        <v>25.1158</v>
+        <v>25.7601</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.83</v>
       </c>
       <c r="I129" t="n">
-        <v>1.4333</v>
+        <v>1.4693</v>
       </c>
       <c r="J129" t="n">
-        <v>24.3661</v>
+        <v>24.9781</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.74</v>
       </c>
       <c r="I130" t="n">
-        <v>1.3314</v>
+        <v>1.3635</v>
       </c>
       <c r="J130" t="n">
-        <v>22.6338</v>
+        <v>23.1795</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1.25</v>
       </c>
       <c r="I131" t="n">
-        <v>0.5693</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="J131" t="n">
-        <v>9.678100000000001</v>
+        <v>9.1936</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.28</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5645</v>
+        <v>0.5052</v>
       </c>
       <c r="J132" t="n">
-        <v>16.3705</v>
+        <v>14.6508</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.19</v>
       </c>
       <c r="I133" t="n">
-        <v>0.4157</v>
+        <v>0.3587</v>
       </c>
       <c r="J133" t="n">
-        <v>12.0553</v>
+        <v>10.4023</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.98</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.043</v>
+        <v>-0.0326</v>
       </c>
       <c r="J134" t="n">
-        <v>-1.247</v>
+        <v>-0.9454</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.83</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2226</v>
+        <v>-0.202</v>
       </c>
       <c r="J135" t="n">
-        <v>-6.4554</v>
+        <v>-5.858</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.74</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3108</v>
+        <v>-0.2935</v>
       </c>
       <c r="J136" t="n">
-        <v>-9.013199999999999</v>
+        <v>-8.5115</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.61</v>
       </c>
       <c r="I137" t="n">
-        <v>1.268</v>
+        <v>1.288</v>
       </c>
       <c r="J137" t="n">
-        <v>36.772</v>
+        <v>37.352</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.17</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4855</v>
+        <v>0.4479</v>
       </c>
       <c r="J138" t="n">
-        <v>14.0795</v>
+        <v>12.9891</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.16</v>
       </c>
       <c r="I139" t="n">
-        <v>0.4627</v>
+        <v>0.4252</v>
       </c>
       <c r="J139" t="n">
-        <v>13.4183</v>
+        <v>12.3308</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.08</v>
       </c>
       <c r="I140" t="n">
-        <v>0.2658</v>
+        <v>0.2333</v>
       </c>
       <c r="J140" t="n">
-        <v>7.7082</v>
+        <v>6.7657</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.7</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.8359</v>
+        <v>-0.8174</v>
       </c>
       <c r="J141" t="n">
-        <v>-24.2411</v>
+        <v>-23.7046</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.25</v>
       </c>
       <c r="I142" t="n">
-        <v>0.6649</v>
+        <v>0.6306</v>
       </c>
       <c r="J142" t="n">
-        <v>17.9523</v>
+        <v>17.0262</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.15</v>
       </c>
       <c r="I143" t="n">
-        <v>0.4423</v>
+        <v>0.4038</v>
       </c>
       <c r="J143" t="n">
-        <v>11.9421</v>
+        <v>10.9026</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.13</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3952</v>
+        <v>0.3574</v>
       </c>
       <c r="J144" t="n">
-        <v>10.6704</v>
+        <v>9.649800000000001</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.12</v>
       </c>
       <c r="I145" t="n">
-        <v>0.3715</v>
+        <v>0.3341</v>
       </c>
       <c r="J145" t="n">
-        <v>10.0305</v>
+        <v>9.0207</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.97</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1578</v>
+        <v>-0.1263</v>
       </c>
       <c r="J146" t="n">
-        <v>-4.2606</v>
+        <v>-3.4101</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.27</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5545</v>
+        <v>0.4957</v>
       </c>
       <c r="J147" t="n">
-        <v>14.9715</v>
+        <v>13.3839</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.23</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4888</v>
+        <v>0.4302</v>
       </c>
       <c r="J148" t="n">
-        <v>13.1976</v>
+        <v>11.6154</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.05</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1506</v>
+        <v>0.1158</v>
       </c>
       <c r="J149" t="n">
-        <v>4.0662</v>
+        <v>3.1266</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.75</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2993</v>
+        <v>-0.2813</v>
       </c>
       <c r="J150" t="n">
-        <v>-8.081099999999999</v>
+        <v>-7.5951</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.61</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4269</v>
+        <v>-0.4193</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.5263</v>
+        <v>-11.3211</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>2.05</v>
       </c>
       <c r="I152" t="n">
-        <v>1.7223</v>
+        <v>1.772</v>
       </c>
       <c r="J152" t="n">
-        <v>36.1683</v>
+        <v>37.212</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.55</v>
       </c>
       <c r="I153" t="n">
-        <v>1.1241</v>
+        <v>1.1428</v>
       </c>
       <c r="J153" t="n">
-        <v>23.6061</v>
+        <v>23.9988</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.4</v>
       </c>
       <c r="I154" t="n">
-        <v>0.9038</v>
+        <v>0.9008</v>
       </c>
       <c r="J154" t="n">
-        <v>18.9798</v>
+        <v>18.9168</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.38</v>
       </c>
       <c r="I155" t="n">
-        <v>0.8665</v>
+        <v>0.8605</v>
       </c>
       <c r="J155" t="n">
-        <v>18.1965</v>
+        <v>18.0705</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.21</v>
       </c>
       <c r="I156" t="n">
-        <v>0.5226</v>
+        <v>0.4945</v>
       </c>
       <c r="J156" t="n">
-        <v>10.9746</v>
+        <v>10.3845</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>0.97</v>
       </c>
       <c r="I157" t="n">
-        <v>0.0064</v>
+        <v>0.0363</v>
       </c>
       <c r="J157" t="n">
-        <v>0.1344</v>
+        <v>0.7623</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.73</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.2814</v>
+        <v>-0.2688</v>
       </c>
       <c r="J158" t="n">
-        <v>-5.9094</v>
+        <v>-5.6448</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.4329</v>
+        <v>-0.4252</v>
       </c>
       <c r="J159" t="n">
-        <v>-9.0909</v>
+        <v>-8.9292</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.54</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4505</v>
+        <v>-0.444</v>
       </c>
       <c r="J160" t="n">
-        <v>-9.4605</v>
+        <v>-9.324</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.39</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5823</v>
+        <v>-0.5913</v>
       </c>
       <c r="J161" t="n">
-        <v>-12.2283</v>
+        <v>-12.4173</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I162" t="n">
-        <v>-0.2042</v>
+        <v>-0.1888</v>
       </c>
       <c r="J162" t="n">
-        <v>-4.084</v>
+        <v>-3.776</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.72</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.2948</v>
+        <v>-0.2822</v>
       </c>
       <c r="J163" t="n">
-        <v>-5.896</v>
+        <v>-5.644</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.67</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.3403</v>
+        <v>-0.3286</v>
       </c>
       <c r="J164" t="n">
-        <v>-6.806</v>
+        <v>-6.572</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.67</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3403</v>
+        <v>-0.3286</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.806</v>
+        <v>-6.572</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.43</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5501</v>
+        <v>-0.5546</v>
       </c>
       <c r="J166" t="n">
-        <v>-11.002</v>
+        <v>-11.092</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.62</v>
       </c>
       <c r="I167" t="n">
-        <v>1.2189</v>
+        <v>1.2369</v>
       </c>
       <c r="J167" t="n">
-        <v>24.378</v>
+        <v>24.738</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.5</v>
       </c>
       <c r="I168" t="n">
-        <v>1.0658</v>
+        <v>1.0797</v>
       </c>
       <c r="J168" t="n">
-        <v>21.316</v>
+        <v>21.594</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.44</v>
       </c>
       <c r="I169" t="n">
-        <v>0.9798</v>
+        <v>0.9829</v>
       </c>
       <c r="J169" t="n">
-        <v>19.596</v>
+        <v>19.658</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.41</v>
       </c>
       <c r="I170" t="n">
-        <v>0.9295</v>
+        <v>0.9265</v>
       </c>
       <c r="J170" t="n">
-        <v>18.59</v>
+        <v>18.53</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.29</v>
       </c>
       <c r="I171" t="n">
-        <v>0.7000999999999999</v>
+        <v>0.681</v>
       </c>
       <c r="J171" t="n">
-        <v>14.002</v>
+        <v>13.62</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.61</v>
       </c>
       <c r="I172" t="n">
-        <v>1.258</v>
+        <v>1.2764</v>
       </c>
       <c r="J172" t="n">
-        <v>37.74</v>
+        <v>38.292</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.21</v>
       </c>
       <c r="I173" t="n">
-        <v>0.5687</v>
+        <v>0.5339</v>
       </c>
       <c r="J173" t="n">
-        <v>17.061</v>
+        <v>16.017</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.14</v>
       </c>
       <c r="I174" t="n">
-        <v>0.4128</v>
+        <v>0.3775</v>
       </c>
       <c r="J174" t="n">
-        <v>12.384</v>
+        <v>11.325</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.04</v>
       </c>
       <c r="I175" t="n">
-        <v>0.1413</v>
+        <v>0.1174</v>
       </c>
       <c r="J175" t="n">
-        <v>4.239</v>
+        <v>3.522</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.9</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3766</v>
+        <v>-0.3351</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.298</v>
+        <v>-10.053</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.08</v>
       </c>
       <c r="I177" t="n">
-        <v>0.2375</v>
+        <v>0.1929</v>
       </c>
       <c r="J177" t="n">
-        <v>7.125</v>
+        <v>5.787</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.07</v>
       </c>
       <c r="I178" t="n">
-        <v>0.2159</v>
+        <v>0.1734</v>
       </c>
       <c r="J178" t="n">
-        <v>6.477</v>
+        <v>5.202</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.0771</v>
       </c>
       <c r="J179" t="n">
-        <v>-2.727</v>
+        <v>-2.313</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.82</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2217</v>
+        <v>-0.2022</v>
       </c>
       <c r="J180" t="n">
-        <v>-6.651</v>
+        <v>-6.066</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.52</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4967</v>
+        <v>-0.4964</v>
       </c>
       <c r="J181" t="n">
-        <v>-14.901</v>
+        <v>-14.892</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.54</v>
       </c>
       <c r="I182" t="n">
-        <v>1.1288</v>
+        <v>1.1429</v>
       </c>
       <c r="J182" t="n">
-        <v>23.7048</v>
+        <v>24.0009</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.46</v>
       </c>
       <c r="I183" t="n">
-        <v>1.0195</v>
+        <v>1.0241</v>
       </c>
       <c r="J183" t="n">
-        <v>21.4095</v>
+        <v>21.5061</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.37</v>
       </c>
       <c r="I184" t="n">
-        <v>0.8652</v>
+        <v>0.8526</v>
       </c>
       <c r="J184" t="n">
-        <v>18.1692</v>
+        <v>17.9046</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.3</v>
       </c>
       <c r="I185" t="n">
-        <v>0.7323</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="J185" t="n">
-        <v>15.3783</v>
+        <v>14.9562</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.14</v>
       </c>
       <c r="I186" t="n">
-        <v>0.3847</v>
+        <v>0.3529</v>
       </c>
       <c r="J186" t="n">
-        <v>8.0787</v>
+        <v>7.4109</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.36</v>
       </c>
       <c r="I187" t="n">
-        <v>0.8041</v>
+        <v>0.7827</v>
       </c>
       <c r="J187" t="n">
-        <v>16.8861</v>
+        <v>16.4367</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2202</v>
+        <v>-0.2043</v>
       </c>
       <c r="J188" t="n">
-        <v>-4.6242</v>
+        <v>-4.2903</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.65</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.3678</v>
+        <v>-0.3543</v>
       </c>
       <c r="J189" t="n">
-        <v>-7.7238</v>
+        <v>-7.4403</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.62</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3947</v>
+        <v>-0.3829</v>
       </c>
       <c r="J190" t="n">
-        <v>-8.2887</v>
+        <v>-8.040900000000001</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.33</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.6463</v>
+        <v>-0.6683</v>
       </c>
       <c r="J191" t="n">
-        <v>-13.5723</v>
+        <v>-14.0343</v>
       </c>
     </row>
   </sheetData>
